--- a/data/personalia/2 BD.xlsx
+++ b/data/personalia/2 BD.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/047618f1b9410114/Desktop/p3ste-app/Fix/Personalia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\3. TSSP.3\18. STE APP\Personalia\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{210E0966-85EC-4AA5-892B-5FB09D7F384E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF5E4D57-964D-46E6-B4A9-90EC443EBF33}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39DAA319-AF4C-41B3-B000-BF45BCE6B35E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,10 +17,19 @@
     <sheet name="LIST_DATA" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$142</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Template Personalia'!$A$1:$T$199</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -29,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="329">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="377">
   <si>
     <t>Wilayah</t>
   </si>
@@ -163,55 +172,187 @@
     <t>Kaur UPT Workshop</t>
   </si>
   <si>
+    <t>WS LAA Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.4 Thb</t>
+  </si>
+  <si>
+    <t>Teknisi</t>
+  </si>
+  <si>
+    <t>LAA 1.1 Rk</t>
+  </si>
+  <si>
+    <t>LAA 1.14 Nmo</t>
+  </si>
+  <si>
+    <t>LAA 1.2 Prp</t>
+  </si>
+  <si>
+    <t>LAA 1.3 Srp</t>
+  </si>
+  <si>
+    <t>LAA 1.5 Du</t>
+  </si>
+  <si>
+    <t>LAA 1.11 Psm</t>
+  </si>
+  <si>
+    <t>LAA 1.6 Jakk</t>
+  </si>
+  <si>
+    <t>LAA 1.7 Pse</t>
+  </si>
+  <si>
+    <t>LAA 1.8 Mri</t>
+  </si>
+  <si>
+    <t>LAA 1.9 Jng</t>
+  </si>
+  <si>
+    <t>LAA 1.10 Ckr</t>
+  </si>
+  <si>
+    <t>LAA 1.12 Dp</t>
+  </si>
+  <si>
+    <t>LAA 1.13 Boo</t>
+  </si>
+  <si>
+    <t>LAA 1.15 Bst</t>
+  </si>
+  <si>
+    <t>PMP Lanjutan</t>
+  </si>
+  <si>
+    <t>PMP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Pelaksana</t>
+  </si>
+  <si>
+    <t>PRP Lanjutan</t>
+  </si>
+  <si>
+    <t>Calon Pekerja</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana</t>
+  </si>
+  <si>
+    <t>Calon Teknisi</t>
+  </si>
+  <si>
+    <t>Calon Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Calon Petugas Negative Check</t>
+  </si>
+  <si>
+    <t>Executive Vice President</t>
+  </si>
+  <si>
+    <t>Kepala UPT BYST</t>
+  </si>
+  <si>
+    <t>Pelaksana Workshop</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Power System 2</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 1</t>
+  </si>
+  <si>
+    <t>Subunit of Field Service Signalling And Communication 2</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop And OCC Signalling and Communication</t>
+  </si>
+  <si>
+    <t>Subunit of Workshop Power System And OCC Power</t>
+  </si>
+  <si>
+    <t>Vice President</t>
+  </si>
+  <si>
+    <t>2 BD</t>
+  </si>
+  <si>
+    <t>SYIHABUDIN</t>
+  </si>
+  <si>
+    <t>Manager STL Daop 2 Bd</t>
+  </si>
+  <si>
+    <t>PMP.240775.00864</t>
+  </si>
+  <si>
+    <t>RIYANTO YANI ARIYADI</t>
+  </si>
+  <si>
+    <t>QC STL 2A Pwk</t>
+  </si>
+  <si>
+    <t>PMP.200678.127160</t>
+  </si>
+  <si>
+    <t>GATOT IMAWAN</t>
+  </si>
+  <si>
+    <t>QC STL 2B Bd</t>
+  </si>
+  <si>
+    <t>PMP.150572.126680</t>
+  </si>
+  <si>
+    <t>RIYADI</t>
+  </si>
+  <si>
+    <t>QC STL 2C Tsm</t>
+  </si>
+  <si>
+    <t>PMP.220976.00882</t>
+  </si>
+  <si>
+    <t>WAHYUDIN</t>
+  </si>
+  <si>
+    <t>AM Informasi dan Evaluasi Daop 2 Bd</t>
+  </si>
+  <si>
+    <t>PMP.300374.71984</t>
+  </si>
+  <si>
+    <t>DANIAL SYAPUTRA</t>
+  </si>
+  <si>
+    <t>AM Kegiatan dan Pembiayaan Daop 2 Bd</t>
+  </si>
+  <si>
+    <t>PRP.160691.00411</t>
+  </si>
+  <si>
+    <t>RIZKI ALI</t>
+  </si>
+  <si>
+    <t>AM Perencanaan Teknis Daop 2 Bd</t>
+  </si>
+  <si>
+    <t>PMP.110788.66920</t>
+  </si>
+  <si>
+    <t>YULIANTI SAFITRI</t>
+  </si>
+  <si>
     <t>Pelaksana Informasi dan Evaluasi</t>
   </si>
   <si>
-    <t>2 BD</t>
-  </si>
-  <si>
-    <t>SYIHABUDIN</t>
-  </si>
-  <si>
-    <t>Manager STL Daop 2 Bd</t>
-  </si>
-  <si>
-    <t>RIYANTO YANI ARIYADI</t>
-  </si>
-  <si>
-    <t>QC STL 2A Pwk</t>
-  </si>
-  <si>
-    <t>GATOT IMAWAN</t>
-  </si>
-  <si>
-    <t>QC STL 2B Bd</t>
-  </si>
-  <si>
-    <t>RIYADI</t>
-  </si>
-  <si>
-    <t>QC STL 2C Tsm</t>
-  </si>
-  <si>
-    <t>WAHYUDIN</t>
-  </si>
-  <si>
-    <t>AM Informasi dan Evaluasi Daop 2 Bd</t>
-  </si>
-  <si>
-    <t>DANIAL SYAPUTRA</t>
-  </si>
-  <si>
-    <t>AM Kegiatan dan Pembiayaan Daop 2 Bd</t>
-  </si>
-  <si>
-    <t>RIZKI ALI</t>
-  </si>
-  <si>
-    <t>AM Perencanaan Teknis Daop 2 Bd</t>
-  </si>
-  <si>
-    <t>YULIANTI SAFITRI</t>
+    <t>PRP.220794.38687</t>
   </si>
   <si>
     <t>SYAHRIR NURZAMZAM</t>
@@ -220,12 +361,18 @@
     <t>Pelaksana Kegiatan dan Pembiayaan Daop 2 Bd</t>
   </si>
   <si>
+    <t>PRP.270593.44954</t>
+  </si>
+  <si>
     <t>REZA NOORMANSYAH PUTRA</t>
   </si>
   <si>
     <t>Pelaksana Perencanaan Teknis Daop 2 Bd</t>
   </si>
   <si>
+    <t>PRP.020592.38688</t>
+  </si>
+  <si>
     <t>FAHMI DARMAWAN WIJAYANTO</t>
   </si>
   <si>
@@ -241,21 +388,27 @@
     <t>Supervisor Perbaikan Workshop Sintelis Bandung</t>
   </si>
   <si>
+    <t>PRP.060592.38591</t>
+  </si>
+  <si>
     <t>DHANY RAMDHANY</t>
   </si>
   <si>
     <t>Supervisor Rekayasa Perawatan Workshop Sintelis Bandung</t>
   </si>
   <si>
+    <t>PRP.090878.125934</t>
+  </si>
+  <si>
     <t>TIAN ANDRIAN SEPTIANDI</t>
   </si>
   <si>
-    <t>Teknisi</t>
-  </si>
-  <si>
     <t>Teknisi Subunit Workshop Rekayasa Perawatan Sintelis Bandung</t>
   </si>
   <si>
+    <t>PRP.070995.38712</t>
+  </si>
+  <si>
     <t>ARIAN BAYU SUGIANTO</t>
   </si>
   <si>
@@ -265,87 +418,147 @@
     <t>2.1 Pwk</t>
   </si>
   <si>
+    <t>PRP.040288.62747</t>
+  </si>
+  <si>
+    <t>PMP.040288.71018</t>
+  </si>
+  <si>
     <t>CECEP SUHENDAR</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 2.1 Pwk</t>
   </si>
   <si>
+    <t>PRP.041286.125941</t>
+  </si>
+  <si>
     <t>MULYADI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 2.1 Pwk</t>
   </si>
   <si>
+    <t>PRP.070688.00336</t>
+  </si>
+  <si>
     <t>ALIT KURNIA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.1 Pwk</t>
   </si>
   <si>
+    <t>PRP.180476.00268</t>
+  </si>
+  <si>
     <t>YOPI CEPI YANTO</t>
   </si>
   <si>
+    <t>PRP.310190.38583</t>
+  </si>
+  <si>
     <t>YOGI SETIAWAN</t>
   </si>
   <si>
+    <t>PRP.090197.38810</t>
+  </si>
+  <si>
     <t>MUHAMMAD BINTANG ARAKA</t>
   </si>
   <si>
+    <t>PRP.100304.57049</t>
+  </si>
+  <si>
     <t>AGUS SUMANTO</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.1 Pwk</t>
   </si>
   <si>
+    <t>PRP.110871.00294</t>
+  </si>
+  <si>
     <t>SYAUQI MAULANA</t>
   </si>
   <si>
+    <t>PRP.280503.71330</t>
+  </si>
+  <si>
     <t>M BAGAS ADITYA</t>
   </si>
   <si>
+    <t>PRP.240102.67502</t>
+  </si>
+  <si>
     <t>Kepala UPT Resor Kelas C 2.2 Rh</t>
   </si>
   <si>
     <t>2.2 Rh</t>
   </si>
   <si>
+    <t>PRP.020274.123300</t>
+  </si>
+  <si>
     <t>DENDA AGUSTINA</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 2.2 Rh</t>
   </si>
   <si>
+    <t>PRP.140886.126586</t>
+  </si>
+  <si>
     <t>LUKMAN SETIAWAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 2.2 Rh</t>
   </si>
   <si>
+    <t>PRP.140978.00275</t>
+  </si>
+  <si>
     <t>ALI AKBAR DAULAY</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.2 Rh</t>
   </si>
   <si>
+    <t>PRP.140673.00329</t>
+  </si>
+  <si>
     <t>MUHAMMAD FAUZI RAMDHANI</t>
   </si>
   <si>
+    <t>PRP.130293.38735</t>
+  </si>
+  <si>
     <t>RUDI ISKANDAR</t>
   </si>
   <si>
+    <t>PRP.190398.71329</t>
+  </si>
+  <si>
     <t>AJI DARMAWAN</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.2 Rh</t>
   </si>
   <si>
+    <t>PRP.120694.38721</t>
+  </si>
+  <si>
     <t>INDRA AMBARI</t>
   </si>
   <si>
+    <t>PRP.290996.38594</t>
+  </si>
+  <si>
     <t>AA SOBARUDIN</t>
   </si>
   <si>
+    <t>PRP.160694.38596</t>
+  </si>
+  <si>
     <t>DIKDIK SOBARI</t>
   </si>
   <si>
@@ -355,36 +568,57 @@
     <t>2.3 Cj</t>
   </si>
   <si>
+    <t>PRP.110774.126470</t>
+  </si>
+  <si>
     <t>SUGIANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 2.3 Cj</t>
   </si>
   <si>
+    <t>PRP.170281.126588</t>
+  </si>
+  <si>
     <t>ARRY TAUFIK RAMDHANI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 2.3 Cj</t>
   </si>
   <si>
+    <t>PRP.240490.00238</t>
+  </si>
+  <si>
     <t>ZAIDAN ADHAM</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.3 Cj</t>
   </si>
   <si>
+    <t>PRP.210404.72308</t>
+  </si>
+  <si>
     <t>GILANG PERMANA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.3 Cj</t>
   </si>
   <si>
+    <t>PRP.151099.66305</t>
+  </si>
+  <si>
     <t>UNDAN HAMDANI</t>
   </si>
   <si>
+    <t>PRP.060191.38809</t>
+  </si>
+  <si>
     <t>NIKO ANDRIAN SYAH</t>
   </si>
   <si>
+    <t>PRP.090103.56724</t>
+  </si>
+  <si>
     <t>INDRA LESMANA</t>
   </si>
   <si>
@@ -394,45 +628,78 @@
     <t>2.4 Cmi</t>
   </si>
   <si>
+    <t>PRP.260888.123401</t>
+  </si>
+  <si>
+    <t>PMP.260888.71982</t>
+  </si>
+  <si>
     <t>WIHARJO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 2.4 Cmi</t>
   </si>
   <si>
+    <t>PRP.090587.00193</t>
+  </si>
+  <si>
     <t>REZHA SEPTIAN FERDIANSYAH</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 2.4 Cmi</t>
   </si>
   <si>
+    <t>PRP.050989.00276</t>
+  </si>
+  <si>
     <t>BAGUS DWI SANTOSO</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.4 Cmi</t>
   </si>
   <si>
+    <t>PRP.200290.00331</t>
+  </si>
+  <si>
     <t>WIKO SYAPUTRA</t>
   </si>
   <si>
+    <t>PRP.080903.71962</t>
+  </si>
+  <si>
     <t>HARTONO</t>
   </si>
   <si>
+    <t>PRP.271088.00273</t>
+  </si>
+  <si>
     <t>BARATA DWI AJI</t>
   </si>
   <si>
+    <t>PRP.191102.71959</t>
+  </si>
+  <si>
     <t>IZAZI</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.4 Cmi</t>
   </si>
   <si>
+    <t>PRP.271072.00274</t>
+  </si>
+  <si>
     <t>ADI MULYANA</t>
   </si>
   <si>
+    <t>PRP.180588.00327</t>
+  </si>
+  <si>
     <t>MAS'UD SHIDDIQ</t>
   </si>
   <si>
+    <t>PRP.120602.75608</t>
+  </si>
+  <si>
     <t>AHMAD HADIAT</t>
   </si>
   <si>
@@ -442,48 +709,84 @@
     <t>2.5 Bd</t>
   </si>
   <si>
+    <t>PRP.180977.00267</t>
+  </si>
+  <si>
+    <t>PMP.180977.122231</t>
+  </si>
+  <si>
     <t>ANDRI SUPRIATNA</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 2.5 Bd</t>
   </si>
   <si>
+    <t>PRP.290387.123371</t>
+  </si>
+  <si>
     <t>SUYONO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 2.5 Bd</t>
   </si>
   <si>
+    <t>PRP.300557.00333</t>
+  </si>
+  <si>
     <t>BERI SUPRIADI</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.5 Bd</t>
   </si>
   <si>
+    <t>PRP.270174.40821</t>
+  </si>
+  <si>
     <t>DARMAWAN SETIADI</t>
   </si>
   <si>
+    <t>PRP.061197.38686</t>
+  </si>
+  <si>
     <t>ASEP LUKMAN</t>
   </si>
   <si>
+    <t>PRP.170871.00296</t>
+  </si>
+  <si>
     <t>ADZKIYA DWI ADI SAPUTRA</t>
   </si>
   <si>
+    <t>PRP.240304.66175</t>
+  </si>
+  <si>
     <t>WIRADENT MORAMA</t>
   </si>
   <si>
+    <t>PRP.050200.69716</t>
+  </si>
+  <si>
     <t>ASEP RISNANDAR</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.5 Bd</t>
   </si>
   <si>
+    <t>PRP.200676.00270</t>
+  </si>
+  <si>
     <t>DANIEL JUNAEDI SAMOSIR</t>
   </si>
   <si>
+    <t>PRP.250699.72007</t>
+  </si>
+  <si>
     <t>RIO APRI NUGROHO</t>
   </si>
   <si>
+    <t>PRP.140404.57050</t>
+  </si>
+  <si>
     <t>SYAEFUL ROHIM</t>
   </si>
   <si>
@@ -493,42 +796,72 @@
     <t>2.6 Kac</t>
   </si>
   <si>
+    <t>PRP.280989.126100</t>
+  </si>
+  <si>
+    <t>PMP.280989.66542</t>
+  </si>
+  <si>
     <t>EKO HANDONO CAHYO P.</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas B 2.6 Kac</t>
   </si>
   <si>
+    <t>PRP.090871.126584</t>
+  </si>
+  <si>
     <t>ISMAWANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas B 2.6 Kac</t>
   </si>
   <si>
+    <t>PRP.150177.125930</t>
+  </si>
+  <si>
     <t>FIRMAN AKBAR NURFAUZI</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.6 Kac</t>
   </si>
   <si>
+    <t>PRP.111196.38684</t>
+  </si>
+  <si>
     <t>ADIN DADANG</t>
   </si>
   <si>
+    <t>PRP.180770.00328</t>
+  </si>
+  <si>
     <t>ANDI GANDA WIJAYA</t>
   </si>
   <si>
+    <t>PRP.110787.00269</t>
+  </si>
+  <si>
     <t>FAJAR HAIDHIN PRABOWO</t>
   </si>
   <si>
+    <t>PRP.100500.66176</t>
+  </si>
+  <si>
     <t>ILHAM SURYA SAPUTRA</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.6 Kac</t>
   </si>
   <si>
+    <t>PRP.150304.57048</t>
+  </si>
+  <si>
     <t>ILMAN KAMIL</t>
   </si>
   <si>
+    <t>PRP.150700.72261</t>
+  </si>
+  <si>
     <t>DIKY NURHIKMAT</t>
   </si>
   <si>
@@ -538,42 +871,72 @@
     <t>2.7 Ng</t>
   </si>
   <si>
+    <t>PRP.221288.123302</t>
+  </si>
+  <si>
+    <t>PMP.221288.69434</t>
+  </si>
+  <si>
     <t>ARIPIN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 2.7 Ng</t>
   </si>
   <si>
+    <t>PRP.020391.00295</t>
+  </si>
+  <si>
     <t>DEDI</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 2.7 Ng</t>
   </si>
   <si>
+    <t>PRP.040275.125933</t>
+  </si>
+  <si>
     <t>JERY ANDRIANUS</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.7 Ng</t>
   </si>
   <si>
+    <t>PRP.190193.38736</t>
+  </si>
+  <si>
     <t>HERI SETIAWAN</t>
   </si>
   <si>
+    <t>PRP.100797.38589</t>
+  </si>
+  <si>
     <t>ABIMANYU HILMY MUCHAMAD</t>
   </si>
   <si>
+    <t>PRP.081199.67654</t>
+  </si>
+  <si>
     <t>MUCHAMAD YUSUF</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.7 Ng</t>
   </si>
   <si>
+    <t>PRP.010677.00373</t>
+  </si>
+  <si>
     <t>RAHMAT RIDO AJI</t>
   </si>
   <si>
+    <t>PRP.02031990.37154</t>
+  </si>
+  <si>
     <t>MUHAMMAD FAJRA SATYA</t>
   </si>
   <si>
+    <t>PRP.090205.75610</t>
+  </si>
+  <si>
     <t>DESTU WAHYU AJI</t>
   </si>
   <si>
@@ -583,48 +946,84 @@
     <t>2.8 Cb</t>
   </si>
   <si>
+    <t>PRP.161281.123370</t>
+  </si>
+  <si>
+    <t>PMP.161281.67008</t>
+  </si>
+  <si>
     <t>RONI KURNIAWAN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 2.8 Cb</t>
   </si>
   <si>
+    <t>PRP.150575.00244</t>
+  </si>
+  <si>
     <t>PANJI SUSANTO</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 2.8 Cb</t>
   </si>
   <si>
+    <t>PRP.130480.125808</t>
+  </si>
+  <si>
     <t>SAHLAN JUANDA SUBAGJA</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.8 Cb</t>
   </si>
   <si>
+    <t>PRP.24011997.38178</t>
+  </si>
+  <si>
     <t>AHMAD RIZKY SETIAWAN</t>
   </si>
   <si>
+    <t>PRP.130998.38717</t>
+  </si>
+  <si>
     <t>AHMAD FARHAN SYUKUR</t>
   </si>
   <si>
+    <t>PRP.130599.74128</t>
+  </si>
+  <si>
     <t>RIZKY FITRIANSYAH</t>
   </si>
   <si>
+    <t>PRP.310198.71961</t>
+  </si>
+  <si>
     <t>ASEP SARIPUDIN</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.8 Cb</t>
   </si>
   <si>
+    <t>PRP.260472.00335</t>
+  </si>
+  <si>
     <t>SAMSUL IRSYAD</t>
   </si>
   <si>
+    <t>PRP.160992.38593</t>
+  </si>
+  <si>
     <t>TOTO ARYANTO</t>
   </si>
   <si>
+    <t>PRP.091189.00245</t>
+  </si>
+  <si>
     <t>MUHAMMAD BAGAS KARA</t>
   </si>
   <si>
+    <t>PRP.071104.71960</t>
+  </si>
+  <si>
     <t>BAGUS SURYONO</t>
   </si>
   <si>
@@ -634,42 +1033,72 @@
     <t>2.9 Tsm</t>
   </si>
   <si>
+    <t>PRP.050881.125809</t>
+  </si>
+  <si>
+    <t>PMP.050881.65346</t>
+  </si>
+  <si>
     <t>LUKMAN RIZAL ARSYAD</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 2.9 Tsm</t>
   </si>
   <si>
+    <t>PRP.201089.00332</t>
+  </si>
+  <si>
     <t>ADIM NURADIM</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 2.9 Tsm</t>
   </si>
   <si>
+    <t>PRP.091278.125932</t>
+  </si>
+  <si>
     <t>DIAN NOVA HEMAWAN</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.9 Tsm</t>
   </si>
   <si>
+    <t>PRP.021197.38719</t>
+  </si>
+  <si>
     <t>IQHBAL WAHYUDHA</t>
   </si>
   <si>
+    <t>PRP.060898.66375</t>
+  </si>
+  <si>
     <t>TULUS HADI PAMUNGKAS</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.9 Tsm</t>
   </si>
   <si>
+    <t>PRP.151286.00304</t>
+  </si>
+  <si>
     <t>MUHAMMAD RIDWAN GOZALI</t>
   </si>
   <si>
+    <t>PRP.060194.38592</t>
+  </si>
+  <si>
     <t>PRI ROCHMAN RAMDHANI</t>
   </si>
   <si>
+    <t>PRP.240198.38582</t>
+  </si>
+  <si>
     <t>MOCHAMAD RIFFA MIFTAH ZAELANI</t>
   </si>
   <si>
+    <t>PRP.160597.38737</t>
+  </si>
+  <si>
     <t>ANDRI PERDIANSYAH</t>
   </si>
   <si>
@@ -679,343 +1108,67 @@
     <t>2.10 Bjr</t>
   </si>
   <si>
+    <t>PRP.020277.127148</t>
+  </si>
+  <si>
     <t>CECEP IMAN NURDIN</t>
   </si>
   <si>
     <t>Supervisor Perawatan Perbaikan UPT Resor Sintelis Kelas C 2.10 Bjr</t>
   </si>
   <si>
+    <t>PRP.160885.126585</t>
+  </si>
+  <si>
     <t>PAJAR TEGAR GUMILANG</t>
   </si>
   <si>
     <t>Supervisor Perawatan Preventif UPT Resor Sintelis Kelas C 2.10 Bjr</t>
   </si>
   <si>
+    <t>PRP.141189.128504</t>
+  </si>
+  <si>
     <t>MUHAMAD SOLEH SYAWALUDIN</t>
   </si>
   <si>
     <t>PNC Perbaikan UPT Resor STL 2.10 Bjr</t>
   </si>
   <si>
+    <t>PRP.270393.38811</t>
+  </si>
+  <si>
     <t>MUH THORIQ EKO NUGROHO</t>
   </si>
   <si>
+    <t>PRP.130599.67504</t>
+  </si>
+  <si>
     <t>IRFANDI MUNANDAR</t>
   </si>
   <si>
+    <t>PRP.061097.67809</t>
+  </si>
+  <si>
     <t>MUHAMMAD DZAKKY RAMADHAN</t>
   </si>
   <si>
     <t>PNC Preventif UPT Resor STL 2.10 Bjr</t>
   </si>
   <si>
+    <t>PRP.241004.75609</t>
+  </si>
+  <si>
     <t>NANA SUMARNA</t>
   </si>
   <si>
+    <t>PRP.010277.00243</t>
+  </si>
+  <si>
     <t>SOLEH ADI</t>
   </si>
   <si>
-    <t>PMP.200678.127160</t>
-  </si>
-  <si>
-    <t>PMP.150572.126680</t>
-  </si>
-  <si>
-    <t>PMP.220976.00882</t>
-  </si>
-  <si>
-    <t>PRP. 300374. 126096</t>
-  </si>
-  <si>
-    <t>PRP.160691.00411</t>
-  </si>
-  <si>
-    <t>PMP.110788.66920</t>
-  </si>
-  <si>
-    <t>PRP.220794.38687</t>
-  </si>
-  <si>
-    <t>PRP.270593.44954</t>
-  </si>
-  <si>
-    <t>PRP.020592.38688</t>
-  </si>
-  <si>
-    <t>PRP.060592.38591</t>
-  </si>
-  <si>
-    <t>PRP.090878.125934</t>
-  </si>
-  <si>
-    <t>PRP.070995.38712</t>
-  </si>
-  <si>
-    <t>PRP.040288.62747</t>
-  </si>
-  <si>
-    <t>PRP.041286.125941</t>
-  </si>
-  <si>
-    <t>PRP.070688.00336</t>
-  </si>
-  <si>
-    <t>PRP.180476.00268</t>
-  </si>
-  <si>
-    <t>PRP.310190.38583</t>
-  </si>
-  <si>
-    <t>PRP.090197.38810</t>
-  </si>
-  <si>
-    <t>PRP.100304.57049</t>
-  </si>
-  <si>
-    <t>PRP.110871.00294</t>
-  </si>
-  <si>
-    <t>PRP.280503.71330</t>
-  </si>
-  <si>
-    <t>PRP.240102.67502</t>
-  </si>
-  <si>
-    <t>PRP.140886.126586</t>
-  </si>
-  <si>
-    <t>PRP.140978.00275</t>
-  </si>
-  <si>
-    <t>PRP.140673.00329</t>
-  </si>
-  <si>
-    <t>PRP.130293.38735</t>
-  </si>
-  <si>
-    <t>PRP.190398.71329</t>
-  </si>
-  <si>
-    <t>PRP.290996.38594</t>
-  </si>
-  <si>
-    <t>PRP.160694.38596</t>
-  </si>
-  <si>
-    <t>PRP.170281.126588</t>
-  </si>
-  <si>
-    <t>PRP.240490.00238</t>
-  </si>
-  <si>
-    <t>PRP.210404.72308</t>
-  </si>
-  <si>
-    <t>PRP.151099.66305</t>
-  </si>
-  <si>
-    <t>PRP.060191.38809</t>
-  </si>
-  <si>
-    <t>PRP.090103.56724</t>
-  </si>
-  <si>
-    <t>PRP.260888.123401</t>
-  </si>
-  <si>
-    <t>PRP.090587.00193</t>
-  </si>
-  <si>
-    <t>PRP.050989.00276</t>
-  </si>
-  <si>
-    <t>PRP.200290.00331</t>
-  </si>
-  <si>
-    <t>PRP.080903.71962</t>
-  </si>
-  <si>
-    <t>PRP.191102.71959</t>
-  </si>
-  <si>
-    <t>PRP.180588.00327</t>
-  </si>
-  <si>
-    <t>PRP.120602.75608</t>
-  </si>
-  <si>
-    <t>PRP.180977.00267</t>
-  </si>
-  <si>
-    <t>PRP.300557.00333</t>
-  </si>
-  <si>
-    <t>PRP.270174.40821</t>
-  </si>
-  <si>
-    <t>PRP.061197.38686</t>
-  </si>
-  <si>
-    <t>PRP.170871.00296</t>
-  </si>
-  <si>
-    <t>PRP.240304.66175</t>
-  </si>
-  <si>
-    <t>PRP.050200.69716</t>
-  </si>
-  <si>
-    <t>PRP.250699.72007</t>
-  </si>
-  <si>
-    <t>PRP.140404.57050</t>
-  </si>
-  <si>
-    <t>PRP.280989.126100</t>
-  </si>
-  <si>
-    <t>PRP.150177.125930</t>
-  </si>
-  <si>
-    <t>PRP.111196.38684</t>
-  </si>
-  <si>
-    <t>PRP.180770.00328</t>
-  </si>
-  <si>
-    <t>PRP.110787.00269</t>
-  </si>
-  <si>
-    <t>PRP.100500.66176</t>
-  </si>
-  <si>
-    <t>PRP.150304.57048</t>
-  </si>
-  <si>
-    <t>PRP.150700.72261</t>
-  </si>
-  <si>
-    <t>PRP.221288.123302</t>
-  </si>
-  <si>
-    <t>PRP.020391.00295</t>
-  </si>
-  <si>
-    <t>PRP.040275.125933</t>
-  </si>
-  <si>
-    <t>PRP.100797.38589</t>
-  </si>
-  <si>
-    <t>PRP.081199.67654</t>
-  </si>
-  <si>
-    <t>PRP.010677.00373</t>
-  </si>
-  <si>
-    <t>PRP.02031990.37154</t>
-  </si>
-  <si>
-    <t>PRP.090205.75610</t>
-  </si>
-  <si>
-    <t>PRP.161281.123370</t>
-  </si>
-  <si>
-    <t>PRP.130480.125808</t>
-  </si>
-  <si>
-    <t>PRP.24011997.38178</t>
-  </si>
-  <si>
-    <t>PRP.130998.38717</t>
-  </si>
-  <si>
-    <t>PRP.130599.74128</t>
-  </si>
-  <si>
-    <t>PRP.310198.71961</t>
-  </si>
-  <si>
-    <t>PRP.260472.00335</t>
-  </si>
-  <si>
-    <t>PRP.160992.38593</t>
-  </si>
-  <si>
-    <t>PRP.091189.00245</t>
-  </si>
-  <si>
-    <t>PRP.071104.71960</t>
-  </si>
-  <si>
-    <t>PRP.050881.125809</t>
-  </si>
-  <si>
-    <t>PRP.091278.125932</t>
-  </si>
-  <si>
-    <t>PRP.021197.38719</t>
-  </si>
-  <si>
-    <t>PRP.060898.66375</t>
-  </si>
-  <si>
-    <t>PRP.151286.00304</t>
-  </si>
-  <si>
-    <t>PRP.060194.38592</t>
-  </si>
-  <si>
-    <t>PRP.240198.38582</t>
-  </si>
-  <si>
-    <t>PRP.160597.38737</t>
-  </si>
-  <si>
-    <t>PRP.160885.126585</t>
-  </si>
-  <si>
-    <t>PRP.141189.128504</t>
-  </si>
-  <si>
-    <t>PRP.270393.38811</t>
-  </si>
-  <si>
-    <t>PRP.130599.67504</t>
-  </si>
-  <si>
-    <t>PRP.241004.75609</t>
-  </si>
-  <si>
-    <t>PRP.010277.00243</t>
-  </si>
-  <si>
     <t>PRP.140892.38714</t>
-  </si>
-  <si>
-    <t>PMP.300374.71984</t>
-  </si>
-  <si>
-    <t>PMP.040288.71018</t>
-  </si>
-  <si>
-    <t>PMP.260888.71982</t>
-  </si>
-  <si>
-    <t>PMP.180977.122231</t>
-  </si>
-  <si>
-    <t>PMP.280989.66542</t>
-  </si>
-  <si>
-    <t>PMP.221288.69434</t>
-  </si>
-  <si>
-    <t>PMP.161281.67008</t>
-  </si>
-  <si>
-    <t>PMP.050881.65346</t>
   </si>
 </sst>
 </file>
@@ -1086,9 +1239,6 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1097,8 +1247,11 @@
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1402,30 +1555,29 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T109"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:T200"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="13.15" zeroHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="11.86328125" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.265625" style="3" customWidth="1"/>
     <col min="3" max="3" width="7.86328125" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.59765625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="20.59765625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="32" style="4" customWidth="1"/>
-    <col min="7" max="7" width="8.46484375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="13.1328125" style="6" customWidth="1"/>
+    <col min="4" max="4" width="20.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.53125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="32" style="7" customWidth="1"/>
+    <col min="7" max="7" width="12.1328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.1328125" style="5" customWidth="1"/>
     <col min="9" max="9" width="7.06640625" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.73046875" style="2" customWidth="1"/>
-    <col min="11" max="13" width="13.1328125" style="6" customWidth="1"/>
+    <col min="11" max="13" width="13.1328125" style="5" customWidth="1"/>
     <col min="14" max="14" width="22" style="2" customWidth="1"/>
-    <col min="15" max="15" width="13.1328125" style="6" customWidth="1"/>
+    <col min="15" max="15" width="13.1328125" style="5" customWidth="1"/>
     <col min="16" max="17" width="22" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.1328125" style="6" customWidth="1"/>
-    <col min="19" max="19" width="22" style="2" customWidth="1"/>
-    <col min="20" max="20" width="22" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.1328125" style="5" customWidth="1"/>
+    <col min="19" max="20" width="22" style="2" customWidth="1"/>
     <col min="21" max="16384" width="9.06640625" style="3" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:20" s="4" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1447,7 +1599,7 @@
       <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="6" t="s">
         <v>6</v>
       </c>
       <c r="I1" s="1" t="s">
@@ -1456,19 +1608,19 @@
       <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" s="6" t="s">
         <v>11</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1477,7 +1629,7 @@
       <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="R1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="S1" s="1" t="s">
@@ -1489,10 +1641,10 @@
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>46</v>
+        <v>81</v>
       </c>
       <c r="C2" s="2">
         <v>42273</v>
@@ -1503,13 +1655,13 @@
       <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>47</v>
+      <c r="F2" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>45901</v>
       </c>
       <c r="I2" s="2">
@@ -1518,23 +1670,31 @@
       <c r="J2" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="5">
         <v>34669</v>
       </c>
-      <c r="L2" s="6">
+      <c r="L2" s="5">
         <v>27599</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="5">
         <v>48061</v>
       </c>
-      <c r="S2" s="3"/>
+      <c r="Q2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="R2" s="5">
+        <v>47370</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="C3" s="2">
         <v>45794</v>
@@ -1545,13 +1705,13 @@
       <c r="E3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="4" t="s">
-        <v>49</v>
+      <c r="F3" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>45884</v>
       </c>
       <c r="I3" s="2">
@@ -1560,35 +1720,31 @@
       <c r="J3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="5">
         <v>35490</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="5">
         <v>28661</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="5">
         <v>49126</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="O3" s="6">
+      <c r="Q3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="R3" s="5">
         <v>46937</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="R3" s="6">
-        <v>46937</v>
-      </c>
-      <c r="S3" s="3"/>
+      <c r="S3" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>50</v>
+        <v>87</v>
       </c>
       <c r="C4" s="2">
         <v>44275</v>
@@ -1599,13 +1755,13 @@
       <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>51</v>
+      <c r="F4" s="7" t="s">
+        <v>88</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>45992</v>
       </c>
       <c r="I4" s="2">
@@ -1614,34 +1770,31 @@
       <c r="J4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="5">
         <v>35217</v>
       </c>
-      <c r="L4" s="6">
-        <v>26434</v>
-      </c>
-      <c r="M4" s="6">
+      <c r="L4" s="5">
+        <v>26483</v>
+      </c>
+      <c r="M4" s="5">
         <v>46905</v>
       </c>
-      <c r="N4" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="O4" s="6">
+      <c r="Q4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="R4" s="5">
         <v>46937</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="R4" s="6">
-        <v>46937</v>
+      <c r="S4" s="2" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2">
         <v>46299</v>
@@ -1652,13 +1805,13 @@
       <c r="E5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="4" t="s">
-        <v>53</v>
+      <c r="F5" s="7" t="s">
+        <v>91</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>45550</v>
       </c>
       <c r="I5" s="2">
@@ -1667,35 +1820,31 @@
       <c r="J5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5" s="5">
         <v>35490</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="5">
         <v>28025</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="5">
         <v>48488</v>
       </c>
-      <c r="N5" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="O5" s="6">
+      <c r="Q5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="R5" s="5">
         <v>46937</v>
       </c>
-      <c r="Q5" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="R5" s="6">
-        <v>46937</v>
-      </c>
-      <c r="S5" s="3"/>
+      <c r="S5" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2">
         <v>43815</v>
@@ -1706,13 +1855,13 @@
       <c r="E6" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="4" t="s">
-        <v>55</v>
+      <c r="F6" s="7" t="s">
+        <v>94</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>45945</v>
       </c>
       <c r="I6" s="2">
@@ -1721,35 +1870,31 @@
       <c r="J6" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6" s="5">
         <v>35217</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="5">
         <v>27118</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="5">
         <v>47574</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="O6" s="6">
-        <v>45646</v>
-      </c>
       <c r="Q6" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="R6" s="6">
+        <v>95</v>
+      </c>
+      <c r="R6" s="5">
         <v>47265</v>
       </c>
-      <c r="S6" s="3"/>
+      <c r="S6" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="C7" s="2">
         <v>64460</v>
@@ -1760,13 +1905,13 @@
       <c r="E7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F7" s="4" t="s">
-        <v>57</v>
+      <c r="F7" s="7" t="s">
+        <v>97</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>45992</v>
       </c>
       <c r="I7" s="2">
@@ -1775,29 +1920,31 @@
       <c r="J7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="5">
         <v>41791</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="5">
         <v>33405</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="5">
         <v>53874</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="O7" s="6">
+        <v>98</v>
+      </c>
+      <c r="O7" s="5">
         <v>46433</v>
       </c>
-      <c r="S7" s="3"/>
+      <c r="P7" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2">
         <v>58183</v>
@@ -1808,13 +1955,13 @@
       <c r="E8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>59</v>
+      <c r="F8" s="7" t="s">
+        <v>100</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>45915</v>
       </c>
       <c r="I8" s="2">
@@ -1823,35 +1970,31 @@
       <c r="J8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8" s="5">
         <v>40269</v>
       </c>
-      <c r="L8" s="6">
+      <c r="L8" s="5">
         <v>32335</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="5">
         <v>52810</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="O8" s="6">
+      <c r="Q8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R8" s="5">
         <v>47097</v>
       </c>
-      <c r="Q8" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="R8" s="6">
-        <v>47097</v>
-      </c>
-      <c r="S8" s="3"/>
+      <c r="S8" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>60</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>69151</v>
@@ -1862,14 +2005,14 @@
       <c r="E9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="4" t="s">
-        <v>44</v>
+      <c r="F9" s="7" t="s">
+        <v>103</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="6">
-        <v>44927</v>
+      <c r="H9" s="5">
+        <v>42879</v>
       </c>
       <c r="I9" s="2">
         <v>4</v>
@@ -1877,29 +2020,31 @@
       <c r="J9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9" s="5">
         <v>42562</v>
       </c>
-      <c r="L9" s="6">
+      <c r="L9" s="5">
         <v>34537</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="5">
         <v>55001</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="O9" s="6">
+        <v>104</v>
+      </c>
+      <c r="O9" s="5">
         <v>46407</v>
       </c>
-      <c r="S9" s="3"/>
+      <c r="P9" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="10" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2">
         <v>71310</v>
@@ -1910,14 +2055,14 @@
       <c r="E10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>62</v>
+      <c r="F10" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="6">
-        <v>44927</v>
+      <c r="H10" s="5">
+        <v>43935</v>
       </c>
       <c r="I10" s="2">
         <v>4</v>
@@ -1925,29 +2070,31 @@
       <c r="J10" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10" s="5">
         <v>43075</v>
       </c>
-      <c r="L10" s="6">
+      <c r="L10" s="5">
         <v>34116</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="5">
         <v>54575</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="O10" s="6">
+        <v>107</v>
+      </c>
+      <c r="O10" s="5">
         <v>46550</v>
       </c>
-      <c r="S10" s="3"/>
+      <c r="P10" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>63</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2">
         <v>69839</v>
@@ -1958,14 +2105,14 @@
       <c r="E11" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="4" t="s">
-        <v>64</v>
+      <c r="F11" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="6">
-        <v>44927</v>
+      <c r="H11" s="5">
+        <v>44270</v>
       </c>
       <c r="I11" s="2">
         <v>4</v>
@@ -1973,29 +2120,31 @@
       <c r="J11" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K11" s="6">
+      <c r="K11" s="5">
         <v>42597</v>
       </c>
-      <c r="L11" s="6">
+      <c r="L11" s="5">
         <v>33726</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="5">
         <v>54210</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="O11" s="6">
+        <v>110</v>
+      </c>
+      <c r="O11" s="5">
         <v>46407</v>
       </c>
-      <c r="S11" s="3"/>
+      <c r="P11" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="C12" s="2">
         <v>69544</v>
@@ -2006,13 +2155,13 @@
       <c r="E12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>66</v>
+      <c r="F12" s="7" t="s">
+        <v>112</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H12" s="6">
+        <v>113</v>
+      </c>
+      <c r="H12" s="5">
         <v>45884</v>
       </c>
       <c r="I12" s="2">
@@ -2021,22 +2170,22 @@
       <c r="J12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K12" s="5">
         <v>42562</v>
       </c>
-      <c r="L12" s="6">
+      <c r="L12" s="5">
         <v>34367</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="5">
         <v>54848</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="C13" s="2">
         <v>69103</v>
@@ -2047,13 +2196,13 @@
       <c r="E13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>69</v>
+      <c r="F13" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H13" s="6">
+        <v>113</v>
+      </c>
+      <c r="H13" s="5">
         <v>45884</v>
       </c>
       <c r="I13" s="2">
@@ -2062,29 +2211,31 @@
       <c r="J13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K13" s="5">
         <v>42562</v>
       </c>
-      <c r="L13" s="6">
+      <c r="L13" s="5">
         <v>33730</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="5">
         <v>54210</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="O13" s="6">
+        <v>116</v>
+      </c>
+      <c r="O13" s="5">
         <v>46407</v>
       </c>
-      <c r="S13" s="3"/>
+      <c r="P13" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="14" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2">
         <v>48936</v>
@@ -2095,14 +2246,14 @@
       <c r="E14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>71</v>
+      <c r="F14" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H14" s="6">
-        <v>44927</v>
+        <v>113</v>
+      </c>
+      <c r="H14" s="5">
+        <v>43479</v>
       </c>
       <c r="I14" s="2">
         <v>8</v>
@@ -2110,29 +2261,31 @@
       <c r="J14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14" s="5">
         <v>38899</v>
       </c>
-      <c r="L14" s="6">
+      <c r="L14" s="5">
         <v>28711</v>
       </c>
-      <c r="M14" s="6">
+      <c r="M14" s="5">
         <v>49188</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="O14" s="6">
+        <v>119</v>
+      </c>
+      <c r="O14" s="5">
         <v>46937</v>
       </c>
-      <c r="S14" s="3"/>
+      <c r="P14" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="15" spans="1:20" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="C15" s="2">
         <v>69841</v>
@@ -2141,15 +2294,15 @@
         <v>33</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>74</v>
+        <v>46</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>121</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="H15" s="6">
+        <v>113</v>
+      </c>
+      <c r="H15" s="5">
         <v>45641</v>
       </c>
       <c r="I15" s="2">
@@ -2158,29 +2311,31 @@
       <c r="J15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15" s="5">
         <v>42597</v>
       </c>
-      <c r="L15" s="6">
-        <v>34889</v>
-      </c>
-      <c r="M15" s="6">
-        <v>55366</v>
+      <c r="L15" s="5">
+        <v>34949</v>
+      </c>
+      <c r="M15" s="5">
+        <v>55427</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="O15" s="6">
+        <v>122</v>
+      </c>
+      <c r="O15" s="5">
         <v>46407</v>
       </c>
-      <c r="S15" s="3"/>
+      <c r="P15" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>75</v>
+        <v>123</v>
       </c>
       <c r="C16" s="2">
         <v>70532</v>
@@ -2191,13 +2346,13 @@
       <c r="E16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>76</v>
+      <c r="F16" s="7" t="s">
+        <v>124</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="6">
+        <v>125</v>
+      </c>
+      <c r="H16" s="5">
         <v>45809</v>
       </c>
       <c r="I16" s="2">
@@ -2206,35 +2361,40 @@
       <c r="J16" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16" s="5">
         <v>42646</v>
       </c>
-      <c r="L16" s="6">
-        <v>32177</v>
-      </c>
-      <c r="M16" s="6">
+      <c r="L16" s="5">
+        <v>32235</v>
+      </c>
+      <c r="M16" s="5">
         <v>52657</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="O16" s="6">
+        <v>126</v>
+      </c>
+      <c r="O16" s="5">
         <v>46973</v>
       </c>
+      <c r="P16" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q16" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="R16" s="6">
+        <v>127</v>
+      </c>
+      <c r="R16" s="5">
         <v>47261</v>
       </c>
-      <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="S16" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>128</v>
       </c>
       <c r="C17" s="2">
         <v>49917</v>
@@ -2245,14 +2405,14 @@
       <c r="E17" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>79</v>
+      <c r="F17" s="7" t="s">
+        <v>129</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H17" s="6">
-        <v>46068</v>
+        <v>125</v>
+      </c>
+      <c r="H17" s="5">
+        <v>43922</v>
       </c>
       <c r="I17" s="2">
         <v>7</v>
@@ -2260,29 +2420,31 @@
       <c r="J17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K17" s="6">
+      <c r="K17" s="5">
         <v>39387</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="5">
         <v>31750</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="5">
         <v>52232</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="O17" s="6">
+        <v>130</v>
+      </c>
+      <c r="O17" s="5">
         <v>47114</v>
       </c>
-      <c r="S17" s="3"/>
-    </row>
-    <row r="18" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P17" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="C18" s="2">
         <v>52965</v>
@@ -2293,13 +2455,13 @@
       <c r="E18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>81</v>
+      <c r="F18" s="7" t="s">
+        <v>132</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="6">
+        <v>125</v>
+      </c>
+      <c r="H18" s="5">
         <v>45658</v>
       </c>
       <c r="I18" s="2">
@@ -2308,29 +2470,31 @@
       <c r="J18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="6">
+      <c r="K18" s="5">
         <v>39814</v>
       </c>
-      <c r="L18" s="6">
-        <v>32330</v>
-      </c>
-      <c r="M18" s="6">
-        <v>52810</v>
+      <c r="L18" s="5">
+        <v>32301</v>
+      </c>
+      <c r="M18" s="5">
+        <v>52779</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="O18" s="6">
+        <v>133</v>
+      </c>
+      <c r="O18" s="5">
         <v>47324</v>
       </c>
-      <c r="S18" s="3"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P18" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="C19" s="2">
         <v>50798</v>
@@ -2341,14 +2505,14 @@
       <c r="E19" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>83</v>
+      <c r="F19" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="6">
-        <v>44927</v>
+        <v>125</v>
+      </c>
+      <c r="H19" s="5">
+        <v>42005</v>
       </c>
       <c r="I19" s="2">
         <v>5</v>
@@ -2356,28 +2520,31 @@
       <c r="J19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K19" s="6">
+      <c r="K19" s="5">
         <v>39600</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="5">
         <v>27868</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="5">
         <v>48335</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="O19" s="6">
+        <v>136</v>
+      </c>
+      <c r="O19" s="5">
         <v>46861</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P19" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2">
         <v>69843</v>
@@ -2388,14 +2555,14 @@
       <c r="E20" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>83</v>
+      <c r="F20" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" s="6">
-        <v>44927</v>
+        <v>125</v>
+      </c>
+      <c r="H20" s="5">
+        <v>43356</v>
       </c>
       <c r="I20" s="2">
         <v>5</v>
@@ -2403,29 +2570,31 @@
       <c r="J20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K20" s="6">
+      <c r="K20" s="5">
         <v>42597</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="5">
         <v>32904</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="5">
         <v>53359</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="O20" s="6">
+        <v>138</v>
+      </c>
+      <c r="O20" s="5">
         <v>46407</v>
       </c>
-      <c r="S20" s="3"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P20" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A21" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="C21" s="2">
         <v>70737</v>
@@ -2436,13 +2605,13 @@
       <c r="E21" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="4" t="s">
-        <v>83</v>
+      <c r="F21" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" s="6">
+        <v>125</v>
+      </c>
+      <c r="H21" s="5">
         <v>45748</v>
       </c>
       <c r="I21" s="2">
@@ -2451,35 +2620,31 @@
       <c r="J21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K21" s="6">
+      <c r="K21" s="5">
         <v>42725</v>
       </c>
-      <c r="L21" s="6">
-        <v>35674</v>
-      </c>
-      <c r="M21" s="6">
-        <v>56158</v>
+      <c r="L21" s="5">
+        <v>35439</v>
+      </c>
+      <c r="M21" s="5">
+        <v>55916</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O21" s="6">
+        <v>140</v>
+      </c>
+      <c r="O21" s="5">
         <v>46407</v>
       </c>
-      <c r="Q21" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="R21" s="6">
-        <v>46407</v>
-      </c>
-      <c r="S21" s="3"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P21" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="C22" s="2">
         <v>74628</v>
@@ -2490,13 +2655,13 @@
       <c r="E22" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>83</v>
+      <c r="F22" s="7" t="s">
+        <v>135</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" s="6">
+        <v>125</v>
+      </c>
+      <c r="H22" s="5">
         <v>45231</v>
       </c>
       <c r="I22" s="2">
@@ -2505,29 +2670,31 @@
       <c r="J22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K22" s="6">
+      <c r="K22" s="5">
         <v>44866</v>
       </c>
-      <c r="L22" s="6">
+      <c r="L22" s="5">
         <v>38056</v>
       </c>
-      <c r="M22" s="6">
+      <c r="M22" s="5">
         <v>58532</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="O22" s="6">
+        <v>142</v>
+      </c>
+      <c r="O22" s="5">
         <v>46916</v>
       </c>
-      <c r="S22" s="3"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P22" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>87</v>
+        <v>143</v>
       </c>
       <c r="C23" s="2">
         <v>47965</v>
@@ -2538,14 +2705,14 @@
       <c r="E23" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="4" t="s">
-        <v>88</v>
+      <c r="F23" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="6">
-        <v>44927</v>
+        <v>125</v>
+      </c>
+      <c r="H23" s="5">
+        <v>42005</v>
       </c>
       <c r="I23" s="2">
         <v>5</v>
@@ -2553,29 +2720,31 @@
       <c r="J23" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K23" s="6">
+      <c r="K23" s="5">
         <v>37135</v>
       </c>
-      <c r="L23" s="6">
+      <c r="L23" s="5">
         <v>26156</v>
       </c>
-      <c r="M23" s="6">
+      <c r="M23" s="5">
         <v>46631</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="O23" s="6">
+        <v>145</v>
+      </c>
+      <c r="O23" s="5">
         <v>46861</v>
       </c>
-      <c r="S23" s="3"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P23" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="C24" s="2">
         <v>75211</v>
@@ -2586,13 +2755,13 @@
       <c r="E24" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="4" t="s">
-        <v>88</v>
+      <c r="F24" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H24" s="6">
+        <v>125</v>
+      </c>
+      <c r="H24" s="5">
         <v>45566</v>
       </c>
       <c r="I24" s="2">
@@ -2601,29 +2770,31 @@
       <c r="J24" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K24" s="6">
+      <c r="K24" s="5">
         <v>44866</v>
       </c>
-      <c r="L24" s="6">
+      <c r="L24" s="5">
         <v>37769</v>
       </c>
-      <c r="M24" s="6">
+      <c r="M24" s="5">
         <v>58227</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="O24" s="6">
+        <v>147</v>
+      </c>
+      <c r="O24" s="5">
         <v>47265</v>
       </c>
-      <c r="S24" s="3"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P24" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A25" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>90</v>
+        <v>148</v>
       </c>
       <c r="C25" s="2">
         <v>75289</v>
@@ -2634,13 +2805,13 @@
       <c r="E25" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>88</v>
+      <c r="F25" s="7" t="s">
+        <v>144</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H25" s="6">
+        <v>125</v>
+      </c>
+      <c r="H25" s="5">
         <v>45566</v>
       </c>
       <c r="I25" s="2">
@@ -2649,29 +2820,31 @@
       <c r="J25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K25" s="5">
         <v>44958</v>
       </c>
-      <c r="L25" s="6">
+      <c r="L25" s="5">
         <v>37280</v>
       </c>
-      <c r="M25" s="6">
+      <c r="M25" s="5">
         <v>57742</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="O25" s="6">
+        <v>149</v>
+      </c>
+      <c r="O25" s="5">
         <v>47114</v>
       </c>
-      <c r="S25" s="3"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P25" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>54</v>
+        <v>93</v>
       </c>
       <c r="C26" s="2">
         <v>49548</v>
@@ -2682,14 +2855,14 @@
       <c r="E26" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F26" s="4" t="s">
-        <v>91</v>
+      <c r="F26" s="7" t="s">
+        <v>150</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H26" s="6">
-        <v>46068</v>
+        <v>151</v>
+      </c>
+      <c r="H26" s="5">
+        <v>45689</v>
       </c>
       <c r="I26" s="2">
         <v>8</v>
@@ -2697,23 +2870,31 @@
       <c r="J26" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K26" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L26" s="6">
+      <c r="K26" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L26" s="5">
         <v>27062</v>
       </c>
-      <c r="M26" s="6">
+      <c r="M26" s="5">
         <v>47543</v>
       </c>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N26" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="O26" s="5">
+        <v>46837</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A27" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="C27" s="2">
         <v>49884</v>
@@ -2724,14 +2905,14 @@
       <c r="E27" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>94</v>
+      <c r="F27" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H27" s="6">
-        <v>46068</v>
+        <v>151</v>
+      </c>
+      <c r="H27" s="5">
+        <v>44823</v>
       </c>
       <c r="I27" s="2">
         <v>7</v>
@@ -2739,28 +2920,31 @@
       <c r="J27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K27" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L27" s="6">
+      <c r="K27" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L27" s="5">
         <v>31638</v>
       </c>
-      <c r="M27" s="6">
+      <c r="M27" s="5">
         <v>52110</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="O27" s="6">
+        <v>155</v>
+      </c>
+      <c r="O27" s="5">
         <v>47285</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P27" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="C28" s="2">
         <v>50904</v>
@@ -2771,14 +2955,14 @@
       <c r="E28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F28" s="4" t="s">
-        <v>96</v>
+      <c r="F28" s="7" t="s">
+        <v>157</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H28" s="6">
-        <v>46068</v>
+        <v>151</v>
+      </c>
+      <c r="H28" s="5">
+        <v>45658</v>
       </c>
       <c r="I28" s="2">
         <v>7</v>
@@ -2786,29 +2970,31 @@
       <c r="J28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K28" s="6">
-        <v>39453</v>
-      </c>
-      <c r="L28" s="6">
+      <c r="K28" s="5">
+        <v>39600</v>
+      </c>
+      <c r="L28" s="5">
         <v>28747</v>
       </c>
-      <c r="M28" s="6">
+      <c r="M28" s="5">
         <v>49218</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="O28" s="6">
+        <v>158</v>
+      </c>
+      <c r="O28" s="5">
         <v>47285</v>
       </c>
-      <c r="S28" s="3"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P28" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A29" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="C29" s="2">
         <v>50764</v>
@@ -2819,14 +3005,14 @@
       <c r="E29" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F29" s="4" t="s">
-        <v>98</v>
+      <c r="F29" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H29" s="6">
-        <v>44927</v>
+        <v>151</v>
+      </c>
+      <c r="H29" s="5">
+        <v>42005</v>
       </c>
       <c r="I29" s="2">
         <v>5</v>
@@ -2834,29 +3020,31 @@
       <c r="J29" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K29" s="6">
+      <c r="K29" s="5">
         <v>39600</v>
       </c>
-      <c r="L29" s="6">
+      <c r="L29" s="5">
         <v>26829</v>
       </c>
-      <c r="M29" s="6">
+      <c r="M29" s="5">
         <v>47300</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="O29" s="6">
+        <v>161</v>
+      </c>
+      <c r="O29" s="5">
         <v>47203</v>
       </c>
-      <c r="S29" s="3"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P29" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="C30" s="2">
         <v>68941</v>
@@ -2867,14 +3055,14 @@
       <c r="E30" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F30" s="4" t="s">
-        <v>98</v>
+      <c r="F30" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H30" s="6">
-        <v>44927</v>
+        <v>151</v>
+      </c>
+      <c r="H30" s="5">
+        <v>43356</v>
       </c>
       <c r="I30" s="2">
         <v>5</v>
@@ -2882,29 +3070,31 @@
       <c r="J30" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K30" s="6">
-        <v>42681</v>
-      </c>
-      <c r="L30" s="6">
+      <c r="K30" s="5">
+        <v>42562</v>
+      </c>
+      <c r="L30" s="5">
         <v>34013</v>
       </c>
-      <c r="M30" s="6">
+      <c r="M30" s="5">
         <v>54483</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="O30" s="6">
+        <v>163</v>
+      </c>
+      <c r="O30" s="5">
         <v>46407</v>
       </c>
-      <c r="S30" s="3"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P30" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A31" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>100</v>
+        <v>164</v>
       </c>
       <c r="C31" s="2">
         <v>75079</v>
@@ -2915,13 +3105,13 @@
       <c r="E31" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>98</v>
+      <c r="F31" s="7" t="s">
+        <v>160</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H31" s="6">
+        <v>151</v>
+      </c>
+      <c r="H31" s="5">
         <v>45748</v>
       </c>
       <c r="I31" s="2">
@@ -2930,29 +3120,31 @@
       <c r="J31" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K31" s="6">
+      <c r="K31" s="5">
         <v>44866</v>
       </c>
-      <c r="L31" s="6">
+      <c r="L31" s="5">
         <v>35873</v>
       </c>
-      <c r="M31" s="6">
+      <c r="M31" s="5">
         <v>56340</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="O31" s="6">
+        <v>165</v>
+      </c>
+      <c r="O31" s="5">
         <v>47265</v>
       </c>
-      <c r="S31" s="3"/>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.45">
+      <c r="P31" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>101</v>
+        <v>166</v>
       </c>
       <c r="C32" s="2">
         <v>71293</v>
@@ -2963,13 +3155,13 @@
       <c r="E32" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F32" s="4" t="s">
-        <v>102</v>
+      <c r="F32" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H32" s="6">
+        <v>151</v>
+      </c>
+      <c r="H32" s="5">
         <v>45180</v>
       </c>
       <c r="I32" s="2">
@@ -2978,23 +3170,31 @@
       <c r="J32" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K32" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L32" s="6">
-        <v>34674</v>
-      </c>
-      <c r="M32" s="6">
-        <v>55154</v>
-      </c>
-      <c r="S32" s="3"/>
+      <c r="K32" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L32" s="5">
+        <v>34497</v>
+      </c>
+      <c r="M32" s="5">
+        <v>54970</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="O32" s="5">
+        <v>46407</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A33" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>103</v>
+        <v>169</v>
       </c>
       <c r="C33" s="2">
         <v>71299</v>
@@ -3005,14 +3205,14 @@
       <c r="E33" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F33" s="4" t="s">
-        <v>102</v>
+      <c r="F33" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H33" s="6">
-        <v>44927</v>
+        <v>151</v>
+      </c>
+      <c r="H33" s="5">
+        <v>44136</v>
       </c>
       <c r="I33" s="2">
         <v>5</v>
@@ -3020,28 +3220,31 @@
       <c r="J33" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K33" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L33" s="6">
+      <c r="K33" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L33" s="5">
         <v>35337</v>
       </c>
-      <c r="M33" s="6">
+      <c r="M33" s="5">
         <v>55793</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="O33" s="6">
+        <v>170</v>
+      </c>
+      <c r="O33" s="5">
         <v>46407</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="C34" s="2">
         <v>71291</v>
@@ -3052,14 +3255,14 @@
       <c r="E34" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F34" s="4" t="s">
-        <v>102</v>
+      <c r="F34" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H34" s="6">
-        <v>44927</v>
+        <v>151</v>
+      </c>
+      <c r="H34" s="5">
+        <v>43466</v>
       </c>
       <c r="I34" s="2">
         <v>5</v>
@@ -3067,29 +3270,31 @@
       <c r="J34" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K34" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L34" s="6">
+      <c r="K34" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L34" s="5">
         <v>34501</v>
       </c>
-      <c r="M34" s="6">
+      <c r="M34" s="5">
         <v>54970</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="O34" s="6">
+        <v>172</v>
+      </c>
+      <c r="O34" s="5">
         <v>46407</v>
       </c>
-      <c r="S34" s="3"/>
+      <c r="P34" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A35" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>105</v>
+        <v>173</v>
       </c>
       <c r="C35" s="2">
         <v>48140</v>
@@ -3100,14 +3305,14 @@
       <c r="E35" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>106</v>
+      <c r="F35" s="7" t="s">
+        <v>174</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H35" s="6">
-        <v>46068</v>
+        <v>175</v>
+      </c>
+      <c r="H35" s="5">
+        <v>45884</v>
       </c>
       <c r="I35" s="2">
         <v>8</v>
@@ -3115,23 +3320,31 @@
       <c r="J35" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K35" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L35" s="6">
-        <v>27340</v>
-      </c>
-      <c r="M35" s="6">
-        <v>47818</v>
-      </c>
-      <c r="S35" s="3"/>
+      <c r="K35" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L35" s="5">
+        <v>27221</v>
+      </c>
+      <c r="M35" s="5">
+        <v>47696</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="O35" s="5">
+        <v>46937</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="36" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>108</v>
+        <v>177</v>
       </c>
       <c r="C36" s="2">
         <v>49625</v>
@@ -3142,14 +3355,14 @@
       <c r="E36" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F36" s="4" t="s">
-        <v>109</v>
+      <c r="F36" s="7" t="s">
+        <v>178</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H36" s="6">
-        <v>46068</v>
+        <v>175</v>
+      </c>
+      <c r="H36" s="5">
+        <v>44823</v>
       </c>
       <c r="I36" s="2">
         <v>7</v>
@@ -3157,29 +3370,31 @@
       <c r="J36" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K36" s="6">
+      <c r="K36" s="5">
         <v>39387</v>
       </c>
-      <c r="L36" s="6">
-        <v>29634</v>
-      </c>
-      <c r="M36" s="6">
+      <c r="L36" s="5">
+        <v>29807</v>
+      </c>
+      <c r="M36" s="5">
         <v>50100</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="O36" s="6">
+        <v>179</v>
+      </c>
+      <c r="O36" s="5">
         <v>47265</v>
       </c>
-      <c r="S36" s="3"/>
+      <c r="P36" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="37" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A37" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>110</v>
+        <v>180</v>
       </c>
       <c r="C37" s="2">
         <v>53025</v>
@@ -3190,14 +3405,14 @@
       <c r="E37" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F37" s="4" t="s">
-        <v>111</v>
+      <c r="F37" s="7" t="s">
+        <v>181</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H37" s="6">
-        <v>44927</v>
+        <v>175</v>
+      </c>
+      <c r="H37" s="5">
+        <v>44814</v>
       </c>
       <c r="I37" s="2">
         <v>7</v>
@@ -3205,29 +3420,31 @@
       <c r="J37" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K37" s="6">
+      <c r="K37" s="5">
         <v>39814</v>
       </c>
-      <c r="L37" s="6">
+      <c r="L37" s="5">
         <v>32987</v>
       </c>
-      <c r="M37" s="6">
+      <c r="M37" s="5">
         <v>53448</v>
       </c>
       <c r="N37" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="O37" s="6">
+        <v>182</v>
+      </c>
+      <c r="O37" s="5">
         <v>46697</v>
       </c>
-      <c r="S37" s="3"/>
+      <c r="P37" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
       <c r="C38" s="2">
         <v>75296</v>
@@ -3238,13 +3455,13 @@
       <c r="E38" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>113</v>
+      <c r="F38" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H38" s="6">
+        <v>175</v>
+      </c>
+      <c r="H38" s="5">
         <v>45748</v>
       </c>
       <c r="I38" s="2">
@@ -3253,29 +3470,31 @@
       <c r="J38" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K38" s="6">
+      <c r="K38" s="5">
         <v>44958</v>
       </c>
-      <c r="L38" s="6">
+      <c r="L38" s="5">
         <v>38098</v>
       </c>
-      <c r="M38" s="6">
+      <c r="M38" s="5">
         <v>58562</v>
       </c>
       <c r="N38" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="O38" s="6">
+        <v>185</v>
+      </c>
+      <c r="O38" s="5">
         <v>47285</v>
       </c>
-      <c r="S38" s="3"/>
+      <c r="P38" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A39" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>114</v>
+        <v>186</v>
       </c>
       <c r="C39" s="2">
         <v>74283</v>
@@ -3286,13 +3505,13 @@
       <c r="E39" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F39" s="4" t="s">
-        <v>115</v>
+      <c r="F39" s="7" t="s">
+        <v>187</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H39" s="6">
+        <v>175</v>
+      </c>
+      <c r="H39" s="5">
         <v>45566</v>
       </c>
       <c r="I39" s="2">
@@ -3301,28 +3520,31 @@
       <c r="J39" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K39" s="6">
+      <c r="K39" s="5">
         <v>44652</v>
       </c>
-      <c r="L39" s="6">
-        <v>36448</v>
-      </c>
-      <c r="M39" s="6">
+      <c r="L39" s="5">
+        <v>36438</v>
+      </c>
+      <c r="M39" s="5">
         <v>56919</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="O39" s="6">
+        <v>188</v>
+      </c>
+      <c r="O39" s="5">
         <v>47054</v>
+      </c>
+      <c r="P39" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>116</v>
+        <v>189</v>
       </c>
       <c r="C40" s="2">
         <v>69842</v>
@@ -3333,14 +3555,14 @@
       <c r="E40" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F40" s="4" t="s">
-        <v>113</v>
+      <c r="F40" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H40" s="6">
-        <v>44927</v>
+        <v>175</v>
+      </c>
+      <c r="H40" s="5">
+        <v>44136</v>
       </c>
       <c r="I40" s="2">
         <v>5</v>
@@ -3348,29 +3570,31 @@
       <c r="J40" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K40" s="6">
+      <c r="K40" s="5">
         <v>42597</v>
       </c>
-      <c r="L40" s="6">
-        <v>33390</v>
-      </c>
-      <c r="M40" s="6">
-        <v>53874</v>
+      <c r="L40" s="5">
+        <v>33244</v>
+      </c>
+      <c r="M40" s="5">
+        <v>53724</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="O40" s="6">
+        <v>190</v>
+      </c>
+      <c r="O40" s="5">
         <v>46407</v>
       </c>
-      <c r="S40" s="3"/>
+      <c r="P40" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>117</v>
+        <v>191</v>
       </c>
       <c r="C41" s="2">
         <v>74376</v>
@@ -3381,13 +3605,13 @@
       <c r="E41" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F41" s="4" t="s">
-        <v>113</v>
+      <c r="F41" s="7" t="s">
+        <v>184</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H41" s="6">
+        <v>175</v>
+      </c>
+      <c r="H41" s="5">
         <v>45231</v>
       </c>
       <c r="I41" s="2">
@@ -3396,29 +3620,31 @@
       <c r="J41" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K41" s="6">
+      <c r="K41" s="5">
         <v>44774</v>
       </c>
-      <c r="L41" s="6">
+      <c r="L41" s="5">
         <v>37630</v>
       </c>
-      <c r="M41" s="6">
+      <c r="M41" s="5">
         <v>58107</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="O41" s="6">
+        <v>192</v>
+      </c>
+      <c r="O41" s="5">
         <v>46916</v>
       </c>
-      <c r="S41" s="3"/>
+      <c r="P41" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>118</v>
+        <v>193</v>
       </c>
       <c r="C42" s="2">
         <v>50251</v>
@@ -3429,13 +3655,13 @@
       <c r="E42" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F42" s="4" t="s">
-        <v>119</v>
+      <c r="F42" s="7" t="s">
+        <v>194</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H42" s="6">
+        <v>195</v>
+      </c>
+      <c r="H42" s="5">
         <v>45884</v>
       </c>
       <c r="I42" s="2">
@@ -3444,35 +3670,40 @@
       <c r="J42" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K42" s="6">
+      <c r="K42" s="5">
         <v>39387</v>
       </c>
-      <c r="L42" s="6">
+      <c r="L42" s="5">
         <v>32381</v>
       </c>
-      <c r="M42" s="6">
+      <c r="M42" s="5">
         <v>52841</v>
       </c>
       <c r="N42" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="O42" s="6">
+        <v>196</v>
+      </c>
+      <c r="O42" s="5">
         <v>46851</v>
       </c>
+      <c r="P42" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q42" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="R42" s="6">
+        <v>197</v>
+      </c>
+      <c r="R42" s="5">
         <v>47265</v>
       </c>
-      <c r="S42" s="3"/>
+      <c r="S42" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="43" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A43" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>121</v>
+        <v>198</v>
       </c>
       <c r="C43" s="2">
         <v>55165</v>
@@ -3483,14 +3714,14 @@
       <c r="E43" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F43" s="4" t="s">
-        <v>122</v>
+      <c r="F43" s="7" t="s">
+        <v>199</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H43" s="6">
-        <v>46068</v>
+        <v>195</v>
+      </c>
+      <c r="H43" s="5">
+        <v>45689</v>
       </c>
       <c r="I43" s="2">
         <v>7</v>
@@ -3498,29 +3729,31 @@
       <c r="J43" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K43" s="6">
+      <c r="K43" s="5">
         <v>40163</v>
       </c>
-      <c r="L43" s="6">
-        <v>32025</v>
-      </c>
-      <c r="M43" s="6">
-        <v>52505</v>
+      <c r="L43" s="5">
+        <v>31906</v>
+      </c>
+      <c r="M43" s="5">
+        <v>52383</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="O43" s="6">
+        <v>200</v>
+      </c>
+      <c r="O43" s="5">
         <v>47285</v>
       </c>
-      <c r="S43" s="3"/>
+      <c r="P43" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="44" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>123</v>
+        <v>201</v>
       </c>
       <c r="C44" s="2">
         <v>53000</v>
@@ -3531,13 +3764,13 @@
       <c r="E44" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F44" s="4" t="s">
-        <v>124</v>
+      <c r="F44" s="7" t="s">
+        <v>202</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H44" s="6">
+        <v>195</v>
+      </c>
+      <c r="H44" s="5">
         <v>45689</v>
       </c>
       <c r="I44" s="2">
@@ -3546,29 +3779,31 @@
       <c r="J44" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K44" s="6">
+      <c r="K44" s="5">
         <v>39814</v>
       </c>
-      <c r="L44" s="6">
+      <c r="L44" s="5">
         <v>32756</v>
       </c>
-      <c r="M44" s="6">
+      <c r="M44" s="5">
         <v>53236</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="O44" s="6">
+        <v>203</v>
+      </c>
+      <c r="O44" s="5">
         <v>46851</v>
       </c>
-      <c r="S44" s="3"/>
+      <c r="P44" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A45" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>125</v>
+        <v>204</v>
       </c>
       <c r="C45" s="2">
         <v>53035</v>
@@ -3579,14 +3814,14 @@
       <c r="E45" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F45" s="4" t="s">
-        <v>126</v>
+      <c r="F45" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H45" s="6">
-        <v>44927</v>
+        <v>195</v>
+      </c>
+      <c r="H45" s="5">
+        <v>42755</v>
       </c>
       <c r="I45" s="2">
         <v>5</v>
@@ -3594,29 +3829,31 @@
       <c r="J45" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K45" s="6">
+      <c r="K45" s="5">
         <v>39814</v>
       </c>
-      <c r="L45" s="6">
-        <v>33105</v>
-      </c>
-      <c r="M45" s="6">
+      <c r="L45" s="5">
+        <v>33087</v>
+      </c>
+      <c r="M45" s="5">
         <v>53571</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="O45" s="6">
+        <v>206</v>
+      </c>
+      <c r="O45" s="5">
         <v>47175</v>
       </c>
-      <c r="S45" s="3"/>
+      <c r="P45" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="C46" s="2">
         <v>75295</v>
@@ -3627,13 +3864,13 @@
       <c r="E46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F46" s="4" t="s">
-        <v>126</v>
+      <c r="F46" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H46" s="6">
+        <v>195</v>
+      </c>
+      <c r="H46" s="5">
         <v>45733</v>
       </c>
       <c r="I46" s="2">
@@ -3642,30 +3879,31 @@
       <c r="J46" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K46" s="6">
+      <c r="K46" s="5">
         <v>44958</v>
       </c>
-      <c r="L46" s="6">
+      <c r="L46" s="5">
         <v>37872</v>
       </c>
-      <c r="M46" s="6">
+      <c r="M46" s="5">
         <v>58349</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="O46" s="6">
+        <v>208</v>
+      </c>
+      <c r="O46" s="5">
         <v>47265</v>
       </c>
-      <c r="P46" s="3"/>
-      <c r="S46" s="3"/>
+      <c r="P46" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="47" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A47" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>128</v>
+        <v>209</v>
       </c>
       <c r="C47" s="2">
         <v>54967</v>
@@ -3676,14 +3914,14 @@
       <c r="E47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F47" s="4" t="s">
-        <v>126</v>
+      <c r="F47" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H47" s="6">
-        <v>44927</v>
+        <v>195</v>
+      </c>
+      <c r="H47" s="5">
+        <v>42005</v>
       </c>
       <c r="I47" s="2">
         <v>5</v>
@@ -3691,24 +3929,31 @@
       <c r="J47" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K47" s="6">
+      <c r="K47" s="5">
         <v>40163</v>
       </c>
-      <c r="L47" s="6">
+      <c r="L47" s="5">
         <v>32443</v>
       </c>
-      <c r="M47" s="6">
+      <c r="M47" s="5">
         <v>52902</v>
       </c>
-      <c r="P47" s="3"/>
-      <c r="S47" s="3"/>
+      <c r="N47" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="O47" s="5">
+        <v>46837</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="C48" s="2">
         <v>76878</v>
@@ -3719,13 +3964,13 @@
       <c r="E48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>126</v>
+      <c r="F48" s="7" t="s">
+        <v>205</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H48" s="6">
+        <v>195</v>
+      </c>
+      <c r="H48" s="5">
         <v>45748</v>
       </c>
       <c r="I48" s="2">
@@ -3734,30 +3979,31 @@
       <c r="J48" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K48" s="6">
+      <c r="K48" s="5">
         <v>45289</v>
       </c>
-      <c r="L48" s="6">
+      <c r="L48" s="5">
         <v>37579</v>
       </c>
-      <c r="M48" s="6">
+      <c r="M48" s="5">
         <v>58045</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="O48" s="6">
+        <v>212</v>
+      </c>
+      <c r="O48" s="5">
         <v>47265</v>
       </c>
-      <c r="P48" s="3"/>
-      <c r="S48" s="3"/>
+      <c r="P48" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A49" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>130</v>
+        <v>213</v>
       </c>
       <c r="C49" s="2">
         <v>48040</v>
@@ -3768,13 +4014,13 @@
       <c r="E49" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F49" s="4" t="s">
-        <v>131</v>
+      <c r="F49" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H49" s="6">
+        <v>195</v>
+      </c>
+      <c r="H49" s="5">
         <v>45672</v>
       </c>
       <c r="I49" s="2">
@@ -3783,24 +4029,31 @@
       <c r="J49" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K49" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L49" s="6">
+      <c r="K49" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L49" s="5">
         <v>26599</v>
       </c>
-      <c r="M49" s="6">
+      <c r="M49" s="5">
         <v>47058</v>
       </c>
-      <c r="P49" s="3"/>
-      <c r="S49" s="3"/>
+      <c r="N49" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="O49" s="5">
+        <v>46861</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>132</v>
+        <v>216</v>
       </c>
       <c r="C50" s="2">
         <v>52962</v>
@@ -3811,13 +4064,13 @@
       <c r="E50" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F50" s="4" t="s">
-        <v>131</v>
+      <c r="F50" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H50" s="6">
+        <v>195</v>
+      </c>
+      <c r="H50" s="5">
         <v>45748</v>
       </c>
       <c r="I50" s="2">
@@ -3826,30 +4079,31 @@
       <c r="J50" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K50" s="6">
+      <c r="K50" s="5">
         <v>39814</v>
       </c>
-      <c r="L50" s="6">
+      <c r="L50" s="5">
         <v>32281</v>
       </c>
-      <c r="M50" s="6">
+      <c r="M50" s="5">
         <v>52749</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="O50" s="6">
+        <v>217</v>
+      </c>
+      <c r="O50" s="5">
         <v>46851</v>
       </c>
-      <c r="P50" s="3"/>
-      <c r="S50" s="3"/>
+      <c r="P50" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A51" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>133</v>
+        <v>218</v>
       </c>
       <c r="C51" s="2">
         <v>76881</v>
@@ -3860,13 +4114,13 @@
       <c r="E51" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F51" s="4" t="s">
-        <v>131</v>
+      <c r="F51" s="7" t="s">
+        <v>214</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H51" s="6">
+        <v>195</v>
+      </c>
+      <c r="H51" s="5">
         <v>45870</v>
       </c>
       <c r="I51" s="2">
@@ -3875,30 +4129,31 @@
       <c r="J51" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K51" s="6">
+      <c r="K51" s="5">
         <v>45289</v>
       </c>
-      <c r="L51" s="6">
+      <c r="L51" s="5">
         <v>37419</v>
       </c>
-      <c r="M51" s="6">
+      <c r="M51" s="5">
         <v>57892</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="O51" s="6">
+        <v>219</v>
+      </c>
+      <c r="O51" s="5">
         <v>47370</v>
       </c>
-      <c r="P51" s="3"/>
-      <c r="S51" s="3"/>
+      <c r="P51" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
       <c r="C52" s="2">
         <v>48890</v>
@@ -3909,13 +4164,13 @@
       <c r="E52" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F52" s="4" t="s">
-        <v>135</v>
+      <c r="F52" s="7" t="s">
+        <v>221</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H52" s="6">
+        <v>222</v>
+      </c>
+      <c r="H52" s="5">
         <v>45870</v>
       </c>
       <c r="I52" s="2">
@@ -3924,36 +4179,40 @@
       <c r="J52" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K52" s="6">
-        <v>38724</v>
-      </c>
-      <c r="L52" s="6">
+      <c r="K52" s="5">
+        <v>38899</v>
+      </c>
+      <c r="L52" s="5">
         <v>28386</v>
       </c>
-      <c r="M52" s="6">
+      <c r="M52" s="5">
         <v>48853</v>
       </c>
       <c r="N52" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="O52" s="6">
+        <v>223</v>
+      </c>
+      <c r="O52" s="5">
         <v>46448</v>
       </c>
-      <c r="P52" s="3"/>
+      <c r="P52" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q52" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="R52" s="6">
+        <v>224</v>
+      </c>
+      <c r="R52" s="5">
         <v>47203</v>
       </c>
-      <c r="S52" s="3"/>
+      <c r="S52" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="53" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A53" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>137</v>
+        <v>225</v>
       </c>
       <c r="C53" s="2">
         <v>49973</v>
@@ -3964,14 +4223,14 @@
       <c r="E53" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F53" s="4" t="s">
-        <v>138</v>
+      <c r="F53" s="7" t="s">
+        <v>226</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H53" s="6">
-        <v>44927</v>
+        <v>222</v>
+      </c>
+      <c r="H53" s="5">
+        <v>44823</v>
       </c>
       <c r="I53" s="2">
         <v>8</v>
@@ -3979,24 +4238,31 @@
       <c r="J53" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K53" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L53" s="6">
+      <c r="K53" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L53" s="5">
         <v>31865</v>
       </c>
-      <c r="M53" s="6">
+      <c r="M53" s="5">
         <v>52322</v>
       </c>
-      <c r="P53" s="3"/>
-      <c r="S53" s="3"/>
+      <c r="N53" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="O53" s="5">
+        <v>46861</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="54" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>139</v>
+        <v>228</v>
       </c>
       <c r="C54" s="2">
         <v>48263</v>
@@ -4007,13 +4273,13 @@
       <c r="E54" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F54" s="4" t="s">
-        <v>140</v>
+      <c r="F54" s="7" t="s">
+        <v>229</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H54" s="6">
+        <v>222</v>
+      </c>
+      <c r="H54" s="5">
         <v>45149</v>
       </c>
       <c r="I54" s="2">
@@ -4022,30 +4288,31 @@
       <c r="J54" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K54" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L54" s="6">
+      <c r="K54" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L54" s="5">
         <v>28275</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M54" s="5">
         <v>48731</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="O54" s="6">
+        <v>230</v>
+      </c>
+      <c r="O54" s="5">
         <v>46742</v>
       </c>
-      <c r="P54" s="3"/>
-      <c r="S54" s="3"/>
+      <c r="P54" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A55" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="C55" s="2">
         <v>50775</v>
@@ -4056,14 +4323,14 @@
       <c r="E55" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F55" s="4" t="s">
-        <v>142</v>
+      <c r="F55" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H55" s="6">
-        <v>44927</v>
+        <v>222</v>
+      </c>
+      <c r="H55" s="5">
+        <v>42005</v>
       </c>
       <c r="I55" s="2">
         <v>5</v>
@@ -4071,30 +4338,31 @@
       <c r="J55" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K55" s="6">
-        <v>39453</v>
-      </c>
-      <c r="L55" s="6">
+      <c r="K55" s="5">
+        <v>39600</v>
+      </c>
+      <c r="L55" s="5">
         <v>27056</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M55" s="5">
         <v>47515</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="O55" s="6">
+        <v>233</v>
+      </c>
+      <c r="O55" s="5">
         <v>46433</v>
       </c>
-      <c r="P55" s="3"/>
-      <c r="S55" s="3"/>
+      <c r="P55" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>143</v>
+        <v>234</v>
       </c>
       <c r="C56" s="2">
         <v>70253</v>
@@ -4105,13 +4373,13 @@
       <c r="E56" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F56" s="4" t="s">
-        <v>142</v>
+      <c r="F56" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H56" s="6">
+        <v>222</v>
+      </c>
+      <c r="H56" s="5">
         <v>44963</v>
       </c>
       <c r="I56" s="2">
@@ -4120,30 +4388,31 @@
       <c r="J56" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K56" s="6">
-        <v>42380</v>
-      </c>
-      <c r="L56" s="6">
-        <v>35592</v>
-      </c>
-      <c r="M56" s="6">
-        <v>56066</v>
+      <c r="K56" s="5">
+        <v>42675</v>
+      </c>
+      <c r="L56" s="5">
+        <v>35740</v>
+      </c>
+      <c r="M56" s="5">
+        <v>56219</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="O56" s="6">
+        <v>235</v>
+      </c>
+      <c r="O56" s="5">
         <v>46407</v>
       </c>
-      <c r="P56" s="3"/>
-      <c r="S56" s="3"/>
+      <c r="P56" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A57" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>144</v>
+        <v>236</v>
       </c>
       <c r="C57" s="2">
         <v>47968</v>
@@ -4154,14 +4423,14 @@
       <c r="E57" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F57" s="4" t="s">
-        <v>142</v>
+      <c r="F57" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H57" s="6">
-        <v>44927</v>
+        <v>222</v>
+      </c>
+      <c r="H57" s="5">
+        <v>42874</v>
       </c>
       <c r="I57" s="2">
         <v>5</v>
@@ -4169,30 +4438,31 @@
       <c r="J57" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K57" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L57" s="6">
+      <c r="K57" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L57" s="5">
         <v>26160</v>
       </c>
-      <c r="M57" s="6">
+      <c r="M57" s="5">
         <v>46631</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="O57" s="6">
+        <v>237</v>
+      </c>
+      <c r="O57" s="5">
         <v>46861</v>
       </c>
-      <c r="P57" s="3"/>
-      <c r="S57" s="3"/>
+      <c r="P57" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>145</v>
+        <v>238</v>
       </c>
       <c r="C58" s="2">
         <v>74372</v>
@@ -4203,13 +4473,13 @@
       <c r="E58" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F58" s="4" t="s">
-        <v>142</v>
+      <c r="F58" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H58" s="6">
+        <v>222</v>
+      </c>
+      <c r="H58" s="5">
         <v>45566</v>
       </c>
       <c r="I58" s="2">
@@ -4218,30 +4488,31 @@
       <c r="J58" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K58" s="6">
+      <c r="K58" s="5">
         <v>44774</v>
       </c>
-      <c r="L58" s="6">
+      <c r="L58" s="5">
         <v>38070</v>
       </c>
-      <c r="M58" s="6">
+      <c r="M58" s="5">
         <v>58532</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="O58" s="6">
+        <v>239</v>
+      </c>
+      <c r="O58" s="5">
         <v>47054</v>
       </c>
-      <c r="P58" s="3"/>
-      <c r="S58" s="3"/>
+      <c r="P58" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="59" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A59" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>146</v>
+        <v>240</v>
       </c>
       <c r="C59" s="2">
         <v>75222</v>
@@ -4252,13 +4523,13 @@
       <c r="E59" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F59" s="4" t="s">
-        <v>142</v>
+      <c r="F59" s="7" t="s">
+        <v>232</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H59" s="6">
+        <v>222</v>
+      </c>
+      <c r="H59" s="5">
         <v>45566</v>
       </c>
       <c r="I59" s="2">
@@ -4267,30 +4538,31 @@
       <c r="J59" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K59" s="6">
+      <c r="K59" s="5">
         <v>44896</v>
       </c>
-      <c r="L59" s="6">
+      <c r="L59" s="5">
         <v>36561</v>
       </c>
-      <c r="M59" s="6">
+      <c r="M59" s="5">
         <v>57040</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="O59" s="6">
+        <v>241</v>
+      </c>
+      <c r="O59" s="5">
         <v>47232</v>
       </c>
-      <c r="P59" s="3"/>
-      <c r="S59" s="3"/>
+      <c r="P59" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>147</v>
+        <v>242</v>
       </c>
       <c r="C60" s="2">
         <v>58845</v>
@@ -4301,14 +4573,14 @@
       <c r="E60" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F60" s="4" t="s">
-        <v>148</v>
+      <c r="F60" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H60" s="6">
-        <v>44927</v>
+        <v>222</v>
+      </c>
+      <c r="H60" s="5">
+        <v>42675</v>
       </c>
       <c r="I60" s="2">
         <v>5</v>
@@ -4316,24 +4588,31 @@
       <c r="J60" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K60" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L60" s="6">
+      <c r="K60" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L60" s="5">
         <v>27941</v>
       </c>
-      <c r="M60" s="6">
+      <c r="M60" s="5">
         <v>48396</v>
       </c>
-      <c r="P60" s="3"/>
-      <c r="S60" s="3"/>
+      <c r="N60" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="O60" s="5">
+        <v>46937</v>
+      </c>
+      <c r="P60" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>149</v>
+        <v>245</v>
       </c>
       <c r="C61" s="2">
         <v>76879</v>
@@ -4344,13 +4623,13 @@
       <c r="E61" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F61" s="4" t="s">
-        <v>148</v>
+      <c r="F61" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H61" s="6">
+        <v>222</v>
+      </c>
+      <c r="H61" s="5">
         <v>45748</v>
       </c>
       <c r="I61" s="2">
@@ -4359,30 +4638,31 @@
       <c r="J61" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K61" s="6">
+      <c r="K61" s="5">
         <v>45289</v>
       </c>
-      <c r="L61" s="6">
+      <c r="L61" s="5">
         <v>36336</v>
       </c>
-      <c r="M61" s="6">
+      <c r="M61" s="5">
         <v>56796</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="O61" s="6">
+        <v>246</v>
+      </c>
+      <c r="O61" s="5">
         <v>47265</v>
       </c>
-      <c r="P61" s="3"/>
-      <c r="S61" s="3"/>
+      <c r="P61" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="62" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>150</v>
+        <v>247</v>
       </c>
       <c r="C62" s="2">
         <v>74702</v>
@@ -4393,13 +4673,13 @@
       <c r="E62" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F62" s="4" t="s">
-        <v>148</v>
+      <c r="F62" s="7" t="s">
+        <v>243</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="H62" s="6">
+        <v>222</v>
+      </c>
+      <c r="H62" s="5">
         <v>45231</v>
       </c>
       <c r="I62" s="2">
@@ -4408,47 +4688,48 @@
       <c r="J62" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K62" s="6">
+      <c r="K62" s="5">
         <v>44866</v>
       </c>
-      <c r="L62" s="6">
+      <c r="L62" s="5">
         <v>38091</v>
       </c>
-      <c r="M62" s="6">
+      <c r="M62" s="5">
         <v>58562</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="O62" s="6">
+        <v>248</v>
+      </c>
+      <c r="O62" s="5">
         <v>46916</v>
       </c>
-      <c r="P62" s="3"/>
-      <c r="S62" s="3"/>
+      <c r="P62" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="63" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A63" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>151</v>
+        <v>249</v>
       </c>
       <c r="C63" s="2">
         <v>50522</v>
       </c>
-      <c r="D63" s="3" t="s">
+      <c r="D63" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F63" s="4" t="s">
-        <v>152</v>
+      <c r="F63" s="7" t="s">
+        <v>250</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H63" s="8">
+        <v>251</v>
+      </c>
+      <c r="H63" s="5">
         <v>45992</v>
       </c>
       <c r="I63" s="2">
@@ -4457,54 +4738,58 @@
       <c r="J63" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K63" s="6">
+      <c r="K63" s="5">
         <v>39387</v>
       </c>
-      <c r="L63" s="6">
-        <v>32779</v>
-      </c>
-      <c r="M63" s="6">
+      <c r="L63" s="5">
+        <v>32780</v>
+      </c>
+      <c r="M63" s="5">
         <v>53236</v>
       </c>
       <c r="N63" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="O63" s="6">
+        <v>252</v>
+      </c>
+      <c r="O63" s="5">
         <v>46950</v>
       </c>
-      <c r="P63" s="3"/>
+      <c r="P63" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q63" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="R63" s="6">
+        <v>253</v>
+      </c>
+      <c r="R63" s="5">
         <v>47054</v>
       </c>
-      <c r="S63" s="3"/>
+      <c r="S63" s="2" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="64" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>154</v>
+        <v>254</v>
       </c>
       <c r="C64" s="2">
         <v>47964</v>
       </c>
-      <c r="D64" s="3" t="s">
+      <c r="D64" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F64" s="4" t="s">
-        <v>155</v>
+      <c r="F64" s="7" t="s">
+        <v>255</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H64" s="8">
-        <v>44927</v>
+        <v>251</v>
+      </c>
+      <c r="H64" s="5">
+        <v>44823</v>
       </c>
       <c r="I64" s="2">
         <v>8</v>
@@ -4512,41 +4797,48 @@
       <c r="J64" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K64" s="6">
+      <c r="K64" s="5">
         <v>37135</v>
       </c>
-      <c r="L64" s="6">
+      <c r="L64" s="5">
         <v>26154</v>
       </c>
-      <c r="M64" s="6">
+      <c r="M64" s="5">
         <v>46631</v>
       </c>
-      <c r="P64" s="3"/>
-      <c r="S64" s="3"/>
+      <c r="N64" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="O64" s="5">
+        <v>47265</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="65" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A65" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>156</v>
+        <v>257</v>
       </c>
       <c r="C65" s="2">
         <v>45678</v>
       </c>
-      <c r="D65" s="3" t="s">
+      <c r="D65" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F65" s="4" t="s">
-        <v>157</v>
+      <c r="F65" s="7" t="s">
+        <v>258</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H65" s="6">
+        <v>251</v>
+      </c>
+      <c r="H65" s="5">
         <v>45884</v>
       </c>
       <c r="I65" s="2">
@@ -4555,47 +4847,48 @@
       <c r="J65" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K65" s="6">
+      <c r="K65" s="5">
         <v>35490</v>
       </c>
-      <c r="L65" s="6">
+      <c r="L65" s="5">
         <v>28140</v>
       </c>
-      <c r="M65" s="6">
+      <c r="M65" s="5">
         <v>48611</v>
       </c>
       <c r="N65" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="O65" s="6">
+        <v>259</v>
+      </c>
+      <c r="O65" s="5">
         <v>46937</v>
       </c>
-      <c r="P65" s="3"/>
-      <c r="S65" s="3"/>
+      <c r="P65" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="66" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>158</v>
+        <v>260</v>
       </c>
       <c r="C66" s="2">
         <v>70734</v>
       </c>
-      <c r="D66" s="3" t="s">
+      <c r="D66" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F66" s="4" t="s">
-        <v>159</v>
+      <c r="F66" s="7" t="s">
+        <v>261</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H66" s="8">
+        <v>251</v>
+      </c>
+      <c r="H66" s="5">
         <v>45672</v>
       </c>
       <c r="I66" s="2">
@@ -4604,48 +4897,49 @@
       <c r="J66" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K66" s="6">
+      <c r="K66" s="5">
         <v>42725</v>
       </c>
-      <c r="L66" s="6">
-        <v>35380</v>
-      </c>
-      <c r="M66" s="6">
+      <c r="L66" s="5">
+        <v>35745</v>
+      </c>
+      <c r="M66" s="5">
         <v>55854</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="O66" s="6">
+        <v>262</v>
+      </c>
+      <c r="O66" s="5">
         <v>46407</v>
       </c>
-      <c r="P66" s="3"/>
-      <c r="S66" s="3"/>
+      <c r="P66" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="67" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>160</v>
+        <v>263</v>
       </c>
       <c r="C67" s="2">
         <v>48680</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="D67" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>159</v>
+      <c r="F67" s="7" t="s">
+        <v>261</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H67" s="8">
-        <v>44927</v>
+        <v>251</v>
+      </c>
+      <c r="H67" s="5">
+        <v>42580</v>
       </c>
       <c r="I67" s="2">
         <v>5</v>
@@ -4653,48 +4947,49 @@
       <c r="J67" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K67" s="6">
-        <v>38724</v>
-      </c>
-      <c r="L67" s="6">
+      <c r="K67" s="5">
+        <v>38899</v>
+      </c>
+      <c r="L67" s="5">
         <v>25757</v>
       </c>
-      <c r="M67" s="6">
+      <c r="M67" s="5">
         <v>46235</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="O67" s="6">
+        <v>264</v>
+      </c>
+      <c r="O67" s="5">
         <v>46851</v>
       </c>
-      <c r="P67" s="3"/>
-      <c r="S67" s="3"/>
+      <c r="P67" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="68" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>161</v>
+        <v>265</v>
       </c>
       <c r="C68" s="2">
         <v>58846</v>
       </c>
-      <c r="D68" s="3" t="s">
+      <c r="D68" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F68" s="4" t="s">
-        <v>159</v>
+      <c r="F68" s="7" t="s">
+        <v>261</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H68" s="6">
-        <v>44927</v>
+        <v>251</v>
+      </c>
+      <c r="H68" s="5">
+        <v>44814</v>
       </c>
       <c r="I68" s="2">
         <v>5</v>
@@ -4702,47 +4997,48 @@
       <c r="J68" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K68" s="6">
-        <v>40545</v>
-      </c>
-      <c r="L68" s="6">
-        <v>32088</v>
-      </c>
-      <c r="M68" s="6">
-        <v>52566</v>
+      <c r="K68" s="5">
+        <v>40575</v>
+      </c>
+      <c r="L68" s="5">
+        <v>31969</v>
+      </c>
+      <c r="M68" s="5">
+        <v>52444</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="O68" s="6">
+        <v>266</v>
+      </c>
+      <c r="O68" s="5">
         <v>47265</v>
       </c>
-      <c r="P68" s="3"/>
-      <c r="S68" s="3"/>
+      <c r="P68" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="69" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>162</v>
+        <v>267</v>
       </c>
       <c r="C69" s="2">
         <v>75220</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="D69" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F69" s="4" t="s">
-        <v>159</v>
+      <c r="F69" s="7" t="s">
+        <v>261</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H69" s="6">
+        <v>251</v>
+      </c>
+      <c r="H69" s="5">
         <v>45566</v>
       </c>
       <c r="I69" s="2">
@@ -4751,47 +5047,48 @@
       <c r="J69" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K69" s="6">
+      <c r="K69" s="5">
         <v>44896</v>
       </c>
-      <c r="L69" s="6">
+      <c r="L69" s="5">
         <v>36656</v>
       </c>
-      <c r="M69" s="6">
+      <c r="M69" s="5">
         <v>57132</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="O69" s="6">
+        <v>268</v>
+      </c>
+      <c r="O69" s="5">
         <v>47054</v>
       </c>
-      <c r="P69" s="3"/>
-      <c r="S69" s="3"/>
+      <c r="P69" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>163</v>
+        <v>269</v>
       </c>
       <c r="C70" s="2">
         <v>74375</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="D70" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E70" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F70" s="4" t="s">
-        <v>164</v>
+      <c r="F70" s="7" t="s">
+        <v>270</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H70" s="8">
+        <v>251</v>
+      </c>
+      <c r="H70" s="5">
         <v>45748</v>
       </c>
       <c r="I70" s="2">
@@ -4800,47 +5097,48 @@
       <c r="J70" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K70" s="6">
+      <c r="K70" s="5">
         <v>44774</v>
       </c>
-      <c r="L70" s="6">
+      <c r="L70" s="5">
         <v>38061</v>
       </c>
-      <c r="M70" s="6">
+      <c r="M70" s="5">
         <v>58532</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="O70" s="6">
+        <v>271</v>
+      </c>
+      <c r="O70" s="5">
         <v>46916</v>
       </c>
-      <c r="P70" s="3"/>
-      <c r="S70" s="3"/>
+      <c r="P70" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="71" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>165</v>
+        <v>272</v>
       </c>
       <c r="C71" s="2">
         <v>76880</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="D71" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F71" s="4" t="s">
-        <v>164</v>
+      <c r="F71" s="7" t="s">
+        <v>270</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="H71" s="8">
+        <v>251</v>
+      </c>
+      <c r="H71" s="5">
         <v>45748</v>
       </c>
       <c r="I71" s="2">
@@ -4849,47 +5147,48 @@
       <c r="J71" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K71" s="6">
+      <c r="K71" s="5">
         <v>45289</v>
       </c>
-      <c r="L71" s="6">
+      <c r="L71" s="5">
         <v>36722</v>
       </c>
-      <c r="M71" s="6">
+      <c r="M71" s="5">
         <v>57193</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="O71" s="6">
+        <v>273</v>
+      </c>
+      <c r="O71" s="5">
         <v>47285</v>
       </c>
-      <c r="P71" s="3"/>
-      <c r="S71" s="3"/>
+      <c r="P71" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="72" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>166</v>
+        <v>274</v>
       </c>
       <c r="C72" s="2">
         <v>50330</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F72" s="4" t="s">
-        <v>167</v>
+      <c r="F72" s="7" t="s">
+        <v>275</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H72" s="8">
+        <v>276</v>
+      </c>
+      <c r="H72" s="5">
         <v>45149</v>
       </c>
       <c r="I72" s="2">
@@ -4898,53 +5197,57 @@
       <c r="J72" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K72" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L72" s="6">
+      <c r="K72" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L72" s="5">
         <v>32499</v>
       </c>
-      <c r="M72" s="6">
+      <c r="M72" s="5">
         <v>52963</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="O72" s="6">
+        <v>277</v>
+      </c>
+      <c r="O72" s="5">
         <v>46837</v>
       </c>
-      <c r="P72" s="3"/>
+      <c r="P72" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q72" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="R72" s="6">
+        <v>278</v>
+      </c>
+      <c r="R72" s="5">
         <v>47175</v>
       </c>
-      <c r="S72" s="3"/>
+      <c r="S72" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="73" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>169</v>
+        <v>279</v>
       </c>
       <c r="C73" s="2">
         <v>54935</v>
       </c>
-      <c r="D73" s="3" t="s">
+      <c r="D73" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E73" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F73" s="4" t="s">
-        <v>170</v>
+      <c r="F73" s="7" t="s">
+        <v>280</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H73" s="8">
+        <v>276</v>
+      </c>
+      <c r="H73" s="5">
         <v>44998</v>
       </c>
       <c r="I73" s="2">
@@ -4953,47 +5256,48 @@
       <c r="J73" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K73" s="6">
+      <c r="K73" s="5">
         <v>40163</v>
       </c>
-      <c r="L73" s="6">
-        <v>33272</v>
-      </c>
-      <c r="M73" s="6">
-        <v>53752</v>
+      <c r="L73" s="5">
+        <v>33299</v>
+      </c>
+      <c r="M73" s="5">
+        <v>53783</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="O73" s="6">
+        <v>281</v>
+      </c>
+      <c r="O73" s="5">
         <v>46742</v>
       </c>
-      <c r="P73" s="3"/>
-      <c r="S73" s="3"/>
+      <c r="P73" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="74" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>171</v>
+        <v>282</v>
       </c>
       <c r="C74" s="2">
         <v>48169</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D74" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F74" s="4" t="s">
-        <v>172</v>
+      <c r="F74" s="7" t="s">
+        <v>283</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H74" s="8">
+        <v>276</v>
+      </c>
+      <c r="H74" s="5">
         <v>45658</v>
       </c>
       <c r="I74" s="2">
@@ -5002,48 +5306,49 @@
       <c r="J74" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K74" s="6">
+      <c r="K74" s="5">
         <v>37135</v>
       </c>
-      <c r="L74" s="6">
+      <c r="L74" s="5">
         <v>27429</v>
       </c>
-      <c r="M74" s="6">
+      <c r="M74" s="5">
         <v>47908</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="O74" s="6">
+        <v>284</v>
+      </c>
+      <c r="O74" s="5">
         <v>47175</v>
       </c>
-      <c r="P74" s="3"/>
-      <c r="S74" s="3"/>
+      <c r="P74" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="75" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>173</v>
+        <v>285</v>
       </c>
       <c r="C75" s="2">
         <v>69837</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="D75" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>174</v>
+      <c r="F75" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H75" s="8">
-        <v>44927</v>
+        <v>276</v>
+      </c>
+      <c r="H75" s="5">
+        <v>43356</v>
       </c>
       <c r="I75" s="2">
         <v>5</v>
@@ -5051,41 +5356,48 @@
       <c r="J75" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K75" s="6">
+      <c r="K75" s="5">
         <v>42597</v>
       </c>
-      <c r="L75" s="6">
+      <c r="L75" s="5">
         <v>33988</v>
       </c>
-      <c r="M75" s="6">
+      <c r="M75" s="5">
         <v>54455</v>
       </c>
-      <c r="P75" s="3"/>
-      <c r="S75" s="3"/>
+      <c r="N75" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="O75" s="5">
+        <v>46407</v>
+      </c>
+      <c r="P75" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="76" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>175</v>
+        <v>288</v>
       </c>
       <c r="C76" s="2">
         <v>70735</v>
       </c>
-      <c r="D76" s="3" t="s">
+      <c r="D76" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F76" s="4" t="s">
-        <v>174</v>
+      <c r="F76" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H76" s="8">
+        <v>276</v>
+      </c>
+      <c r="H76" s="5">
         <v>45641</v>
       </c>
       <c r="I76" s="2">
@@ -5094,47 +5406,48 @@
       <c r="J76" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K76" s="6">
+      <c r="K76" s="5">
         <v>42725</v>
       </c>
-      <c r="L76" s="6">
+      <c r="L76" s="5">
         <v>35621</v>
       </c>
-      <c r="M76" s="6">
+      <c r="M76" s="5">
         <v>56097</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="O76" s="6">
+        <v>289</v>
+      </c>
+      <c r="O76" s="5">
         <v>46407</v>
       </c>
-      <c r="P76" s="3"/>
-      <c r="S76" s="3"/>
+      <c r="P76" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="77" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>176</v>
+        <v>290</v>
       </c>
       <c r="C77" s="2">
         <v>74353</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="D77" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E77" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F77" s="4" t="s">
-        <v>174</v>
+      <c r="F77" s="7" t="s">
+        <v>286</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H77" s="8">
+        <v>276</v>
+      </c>
+      <c r="H77" s="5">
         <v>45566</v>
       </c>
       <c r="I77" s="2">
@@ -5143,48 +5456,49 @@
       <c r="J77" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K77" s="6">
+      <c r="K77" s="5">
         <v>44774</v>
       </c>
-      <c r="L77" s="6">
+      <c r="L77" s="5">
         <v>36472</v>
       </c>
-      <c r="M77" s="6">
+      <c r="M77" s="5">
         <v>56949</v>
       </c>
       <c r="N77" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="O77" s="6">
+        <v>291</v>
+      </c>
+      <c r="O77" s="5">
         <v>47114</v>
       </c>
-      <c r="P77" s="3"/>
-      <c r="S77" s="3"/>
+      <c r="P77" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="78" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>177</v>
+        <v>292</v>
       </c>
       <c r="C78" s="2">
         <v>48267</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="D78" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E78" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F78" s="4" t="s">
-        <v>178</v>
+      <c r="F78" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H78" s="6">
-        <v>44927</v>
+        <v>276</v>
+      </c>
+      <c r="H78" s="5">
+        <v>42005</v>
       </c>
       <c r="I78" s="2">
         <v>5</v>
@@ -5192,48 +5506,49 @@
       <c r="J78" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K78" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L78" s="6">
-        <v>28131</v>
-      </c>
-      <c r="M78" s="6">
-        <v>48611</v>
+      <c r="K78" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L78" s="5">
+        <v>28277</v>
+      </c>
+      <c r="M78" s="5">
+        <v>48761</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="O78" s="6">
+        <v>294</v>
+      </c>
+      <c r="O78" s="5">
         <v>47114</v>
       </c>
-      <c r="P78" s="3"/>
-      <c r="S78" s="3"/>
+      <c r="P78" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="79" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>179</v>
+        <v>295</v>
       </c>
       <c r="C79" s="2">
         <v>69838</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F79" s="4" t="s">
-        <v>178</v>
+      <c r="F79" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H79" s="6">
-        <v>44927</v>
+        <v>276</v>
+      </c>
+      <c r="H79" s="5">
+        <v>43356</v>
       </c>
       <c r="I79" s="2">
         <v>5</v>
@@ -5241,47 +5556,48 @@
       <c r="J79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K79" s="6">
+      <c r="K79" s="5">
         <v>42597</v>
       </c>
-      <c r="L79" s="6">
-        <v>32907</v>
-      </c>
-      <c r="M79" s="6">
-        <v>53387</v>
+      <c r="L79" s="5">
+        <v>32934</v>
+      </c>
+      <c r="M79" s="5">
+        <v>53418</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="O79" s="6">
+        <v>296</v>
+      </c>
+      <c r="O79" s="5">
         <v>46259</v>
       </c>
-      <c r="P79" s="3"/>
-      <c r="S79" s="3"/>
+      <c r="P79" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="80" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>180</v>
+        <v>297</v>
       </c>
       <c r="C80" s="2">
         <v>76643</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E80" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F80" s="4" t="s">
-        <v>178</v>
+      <c r="F80" s="7" t="s">
+        <v>293</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H80" s="6">
+        <v>276</v>
+      </c>
+      <c r="H80" s="5">
         <v>45748</v>
       </c>
       <c r="I80" s="2">
@@ -5290,47 +5606,48 @@
       <c r="J80" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K80" s="6">
+      <c r="K80" s="5">
         <v>45250</v>
       </c>
-      <c r="L80" s="6">
+      <c r="L80" s="5">
         <v>38392</v>
       </c>
-      <c r="M80" s="6">
+      <c r="M80" s="5">
         <v>58866</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="O80" s="6">
+        <v>298</v>
+      </c>
+      <c r="O80" s="5">
         <v>47370</v>
       </c>
-      <c r="P80" s="3"/>
-      <c r="S80" s="3"/>
+      <c r="P80" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="81" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>181</v>
+        <v>299</v>
       </c>
       <c r="C81" s="2">
         <v>49631</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E81" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F81" s="4" t="s">
-        <v>182</v>
+      <c r="F81" s="7" t="s">
+        <v>300</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H81" s="8">
+        <v>301</v>
+      </c>
+      <c r="H81" s="5">
         <v>45474</v>
       </c>
       <c r="I81" s="2">
@@ -5339,53 +5656,57 @@
       <c r="J81" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K81" s="6">
+      <c r="K81" s="5">
         <v>39387</v>
       </c>
-      <c r="L81" s="6">
+      <c r="L81" s="5">
         <v>29936</v>
       </c>
-      <c r="M81" s="6">
+      <c r="M81" s="5">
         <v>50406</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="O81" s="6">
+        <v>302</v>
+      </c>
+      <c r="O81" s="5">
         <v>47054</v>
       </c>
-      <c r="P81" s="3"/>
+      <c r="P81" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q81" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="R81" s="6">
+        <v>303</v>
+      </c>
+      <c r="R81" s="5">
         <v>47097</v>
       </c>
-      <c r="S81" s="3"/>
+      <c r="S81" s="2" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="82" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>184</v>
+        <v>304</v>
       </c>
       <c r="C82" s="2">
         <v>50810</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F82" s="4" t="s">
-        <v>185</v>
+      <c r="F82" s="7" t="s">
+        <v>305</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H82" s="8">
+        <v>301</v>
+      </c>
+      <c r="H82" s="5">
         <v>45658</v>
       </c>
       <c r="I82" s="2">
@@ -5394,42 +5715,49 @@
       <c r="J82" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K82" s="6">
+      <c r="K82" s="5">
         <v>39600</v>
       </c>
-      <c r="L82" s="6">
-        <v>27529</v>
-      </c>
-      <c r="M82" s="6">
+      <c r="L82" s="5">
+        <v>27421</v>
+      </c>
+      <c r="M82" s="5">
         <v>48000</v>
       </c>
-      <c r="P82" s="3"/>
-      <c r="S82" s="3"/>
+      <c r="N82" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="O82" s="5">
+        <v>46916</v>
+      </c>
+      <c r="P82" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="83" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>186</v>
+        <v>307</v>
       </c>
       <c r="C83" s="2">
         <v>49618</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F83" s="4" t="s">
-        <v>187</v>
+      <c r="F83" s="7" t="s">
+        <v>308</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H83" s="8">
-        <v>44927</v>
+        <v>301</v>
+      </c>
+      <c r="H83" s="5">
+        <v>43661</v>
       </c>
       <c r="I83" s="2">
         <v>7</v>
@@ -5437,47 +5765,48 @@
       <c r="J83" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K83" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L83" s="6">
+      <c r="K83" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L83" s="5">
         <v>29324</v>
       </c>
-      <c r="M83" s="6">
+      <c r="M83" s="5">
         <v>49796</v>
       </c>
       <c r="N83" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="O83" s="6">
+        <v>309</v>
+      </c>
+      <c r="O83" s="5">
         <v>47114</v>
       </c>
-      <c r="P83" s="3"/>
-      <c r="S83" s="3"/>
+      <c r="P83" s="2" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="84" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>188</v>
+        <v>310</v>
       </c>
       <c r="C84" s="2">
         <v>69840</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F84" s="4" t="s">
-        <v>189</v>
+      <c r="F84" s="7" t="s">
+        <v>311</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H84" s="6">
+        <v>301</v>
+      </c>
+      <c r="H84" s="5">
         <v>44963</v>
       </c>
       <c r="I84" s="2">
@@ -5486,47 +5815,48 @@
       <c r="J84" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K84" s="6">
+      <c r="K84" s="5">
         <v>42597</v>
       </c>
-      <c r="L84" s="6">
+      <c r="L84" s="5">
         <v>35454</v>
       </c>
-      <c r="M84" s="6">
+      <c r="M84" s="5">
         <v>55916</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="O84" s="6">
+        <v>312</v>
+      </c>
+      <c r="O84" s="5">
         <v>46305</v>
       </c>
-      <c r="P84" s="3"/>
-      <c r="S84" s="3"/>
+      <c r="P84" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="85" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>190</v>
+        <v>313</v>
       </c>
       <c r="C85" s="2">
         <v>71292</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E85" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F85" s="4" t="s">
-        <v>189</v>
+      <c r="F85" s="7" t="s">
+        <v>311</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H85" s="8">
+        <v>301</v>
+      </c>
+      <c r="H85" s="5">
         <v>45658</v>
       </c>
       <c r="I85" s="2">
@@ -5535,47 +5865,48 @@
       <c r="J85" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K85" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L85" s="6">
+      <c r="K85" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L85" s="5">
         <v>36051</v>
       </c>
-      <c r="M85" s="6">
+      <c r="M85" s="5">
         <v>56523</v>
       </c>
       <c r="N85" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="O85" s="6">
+        <v>314</v>
+      </c>
+      <c r="O85" s="5">
         <v>46407</v>
       </c>
-      <c r="P85" s="3"/>
-      <c r="S85" s="3"/>
+      <c r="P85" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="86" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>191</v>
+        <v>315</v>
       </c>
       <c r="C86" s="2">
         <v>76383</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>189</v>
+      <c r="F86" s="7" t="s">
+        <v>311</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H86" s="6">
+        <v>301</v>
+      </c>
+      <c r="H86" s="5">
         <v>45748</v>
       </c>
       <c r="I86" s="2">
@@ -5584,47 +5915,48 @@
       <c r="J86" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K86" s="6">
+      <c r="K86" s="5">
         <v>45200</v>
       </c>
-      <c r="L86" s="6">
+      <c r="L86" s="5">
         <v>36293</v>
       </c>
-      <c r="M86" s="6">
+      <c r="M86" s="5">
         <v>56766</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="O86" s="6">
+        <v>316</v>
+      </c>
+      <c r="O86" s="5">
         <v>47324</v>
       </c>
-      <c r="P86" s="3"/>
-      <c r="S86" s="3"/>
+      <c r="P86" s="2" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="87" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>192</v>
+        <v>317</v>
       </c>
       <c r="C87" s="2">
         <v>75293</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E87" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>189</v>
+      <c r="F87" s="7" t="s">
+        <v>311</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H87" s="6">
+        <v>301</v>
+      </c>
+      <c r="H87" s="5">
         <v>45748</v>
       </c>
       <c r="I87" s="2">
@@ -5633,46 +5965,49 @@
       <c r="J87" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K87" s="6">
+      <c r="K87" s="5">
         <v>44958</v>
       </c>
-      <c r="L87" s="6">
+      <c r="L87" s="5">
         <v>35826</v>
       </c>
-      <c r="M87" s="6">
+      <c r="M87" s="5">
         <v>56281</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="O87" s="6">
+        <v>318</v>
+      </c>
+      <c r="O87" s="5">
         <v>47265</v>
+      </c>
+      <c r="P87" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="88" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>193</v>
+        <v>319</v>
       </c>
       <c r="C88" s="2">
         <v>48002</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F88" s="4" t="s">
-        <v>194</v>
+      <c r="F88" s="7" t="s">
+        <v>320</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H88" s="6">
-        <v>44927</v>
+        <v>301</v>
+      </c>
+      <c r="H88" s="5">
+        <v>42005</v>
       </c>
       <c r="I88" s="2">
         <v>5</v>
@@ -5680,46 +6015,49 @@
       <c r="J88" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K88" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L88" s="6">
+      <c r="K88" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L88" s="5">
         <v>26415</v>
       </c>
-      <c r="M88" s="6">
+      <c r="M88" s="5">
         <v>46874</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="O88" s="6">
+        <v>321</v>
+      </c>
+      <c r="O88" s="5">
         <v>47324</v>
+      </c>
+      <c r="P88" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="89" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A89" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>195</v>
+        <v>322</v>
       </c>
       <c r="C89" s="2">
         <v>71309</v>
       </c>
-      <c r="D89" s="3" t="s">
+      <c r="D89" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E89" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F89" s="4" t="s">
-        <v>194</v>
+      <c r="F89" s="7" t="s">
+        <v>320</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H89" s="6">
-        <v>44927</v>
+        <v>301</v>
+      </c>
+      <c r="H89" s="5">
+        <v>43466</v>
       </c>
       <c r="I89" s="2">
         <v>5</v>
@@ -5727,46 +6065,49 @@
       <c r="J89" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K89" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L89" s="6">
+      <c r="K89" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L89" s="5">
         <v>33863</v>
       </c>
-      <c r="M89" s="6">
+      <c r="M89" s="5">
         <v>54332</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="O89" s="6">
+        <v>323</v>
+      </c>
+      <c r="O89" s="5">
         <v>46407</v>
+      </c>
+      <c r="P89" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="90" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>196</v>
+        <v>324</v>
       </c>
       <c r="C90" s="2">
         <v>53007</v>
       </c>
-      <c r="D90" s="3" t="s">
+      <c r="D90" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E90" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F90" s="4" t="s">
-        <v>194</v>
+      <c r="F90" s="7" t="s">
+        <v>320</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H90" s="6">
-        <v>44927</v>
+        <v>301</v>
+      </c>
+      <c r="H90" s="5">
+        <v>44631</v>
       </c>
       <c r="I90" s="2">
         <v>5</v>
@@ -5774,45 +6115,48 @@
       <c r="J90" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K90" s="6">
+      <c r="K90" s="5">
         <v>39814</v>
       </c>
-      <c r="L90" s="6">
-        <v>32762</v>
-      </c>
-      <c r="M90" s="6">
-        <v>53236</v>
+      <c r="L90" s="5">
+        <v>32821</v>
+      </c>
+      <c r="M90" s="5">
+        <v>53297</v>
       </c>
       <c r="N90" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="O90" s="6">
+        <v>325</v>
+      </c>
+      <c r="O90" s="5">
         <v>46861</v>
+      </c>
+      <c r="P90" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="91" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>197</v>
+        <v>326</v>
       </c>
       <c r="C91" s="2">
         <v>76641</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D91" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E91" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F91" s="4" t="s">
-        <v>194</v>
+      <c r="F91" s="7" t="s">
+        <v>320</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="H91" s="6">
+        <v>301</v>
+      </c>
+      <c r="H91" s="5">
         <v>45748</v>
       </c>
       <c r="I91" s="2">
@@ -5821,46 +6165,49 @@
       <c r="J91" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K91" s="6">
+      <c r="K91" s="5">
         <v>45250</v>
       </c>
-      <c r="L91" s="6">
+      <c r="L91" s="5">
         <v>38298</v>
       </c>
-      <c r="M91" s="6">
+      <c r="M91" s="5">
         <v>58776</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="O91" s="6">
+        <v>327</v>
+      </c>
+      <c r="O91" s="5">
         <v>47265</v>
+      </c>
+      <c r="P91" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="92" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>198</v>
+        <v>328</v>
       </c>
       <c r="C92" s="2">
         <v>49630</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D92" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>199</v>
+      <c r="F92" s="7" t="s">
+        <v>329</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H92" s="6">
-        <v>46068</v>
+        <v>330</v>
+      </c>
+      <c r="H92" s="5">
+        <v>44823</v>
       </c>
       <c r="I92" s="2">
         <v>8</v>
@@ -5868,51 +6215,57 @@
       <c r="J92" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K92" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L92" s="6">
-        <v>29714</v>
-      </c>
-      <c r="M92" s="6">
-        <v>50192</v>
+      <c r="K92" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L92" s="5">
+        <v>29803</v>
+      </c>
+      <c r="M92" s="5">
+        <v>50284</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="O92" s="6">
+        <v>331</v>
+      </c>
+      <c r="O92" s="5">
         <v>46937</v>
       </c>
+      <c r="P92" s="2" t="s">
+        <v>64</v>
+      </c>
       <c r="Q92" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="R92" s="6">
+        <v>332</v>
+      </c>
+      <c r="R92" s="5">
         <v>47008</v>
+      </c>
+      <c r="S92" s="2" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>201</v>
+        <v>333</v>
       </c>
       <c r="C93" s="2">
         <v>53004</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D93" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>202</v>
+      <c r="F93" s="7" t="s">
+        <v>334</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H93" s="6">
+        <v>330</v>
+      </c>
+      <c r="H93" s="5">
         <v>45658</v>
       </c>
       <c r="I93" s="2">
@@ -5921,40 +6274,49 @@
       <c r="J93" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K93" s="6">
+      <c r="K93" s="5">
         <v>39814</v>
       </c>
-      <c r="L93" s="6">
+      <c r="L93" s="5">
         <v>32801</v>
       </c>
-      <c r="M93" s="6">
+      <c r="M93" s="5">
         <v>53267</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="O93" s="5">
+        <v>46727</v>
+      </c>
+      <c r="P93" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="94" spans="1:19" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>203</v>
+        <v>336</v>
       </c>
       <c r="C94" s="2">
         <v>49602</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D94" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E94" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F94" s="4" t="s">
-        <v>204</v>
+      <c r="F94" s="7" t="s">
+        <v>337</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H94" s="6">
-        <v>44927</v>
+        <v>330</v>
+      </c>
+      <c r="H94" s="5">
+        <v>42781</v>
       </c>
       <c r="I94" s="2">
         <v>7</v>
@@ -5962,46 +6324,49 @@
       <c r="J94" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K94" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L94" s="6">
-        <v>28745</v>
-      </c>
-      <c r="M94" s="6">
-        <v>49218</v>
+      <c r="K94" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L94" s="5">
+        <v>27062</v>
+      </c>
+      <c r="M94" s="5">
+        <v>49310</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="O94" s="6">
+        <v>338</v>
+      </c>
+      <c r="O94" s="5">
         <v>47114</v>
+      </c>
+      <c r="P94" s="2" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="95" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>205</v>
+        <v>339</v>
       </c>
       <c r="C95" s="2">
         <v>70254</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D95" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E95" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F95" s="4" t="s">
-        <v>206</v>
+      <c r="F95" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H95" s="6">
-        <v>44927</v>
+        <v>330</v>
+      </c>
+      <c r="H95" s="5">
+        <v>44348</v>
       </c>
       <c r="I95" s="2">
         <v>5</v>
@@ -6009,45 +6374,48 @@
       <c r="J95" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K95" s="6">
-        <v>42380</v>
-      </c>
-      <c r="L95" s="6">
-        <v>35472</v>
-      </c>
-      <c r="M95" s="6">
-        <v>55944</v>
+      <c r="K95" s="5">
+        <v>42675</v>
+      </c>
+      <c r="L95" s="5">
+        <v>35736</v>
+      </c>
+      <c r="M95" s="5">
+        <v>56219</v>
       </c>
       <c r="N95" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="O95" s="6">
+        <v>341</v>
+      </c>
+      <c r="O95" s="5">
         <v>46407</v>
+      </c>
+      <c r="P95" s="2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="96" spans="1:19" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>207</v>
+        <v>342</v>
       </c>
       <c r="C96" s="2">
         <v>74660</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D96" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E96" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F96" s="4" t="s">
-        <v>206</v>
+      <c r="F96" s="7" t="s">
+        <v>340</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H96" s="6">
+        <v>330</v>
+      </c>
+      <c r="H96" s="5">
         <v>45566</v>
       </c>
       <c r="I96" s="2">
@@ -6056,46 +6424,49 @@
       <c r="J96" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K96" s="6">
+      <c r="K96" s="5">
         <v>44866</v>
       </c>
-      <c r="L96" s="6">
+      <c r="L96" s="5">
         <v>36013</v>
       </c>
-      <c r="M96" s="6">
+      <c r="M96" s="5">
         <v>56493</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="O96" s="6">
+        <v>343</v>
+      </c>
+      <c r="O96" s="5">
         <v>47054</v>
       </c>
-    </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P96" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A97" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>208</v>
+        <v>344</v>
       </c>
       <c r="C97" s="2">
         <v>55010</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D97" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E97" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F97" s="4" t="s">
-        <v>209</v>
+      <c r="F97" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H97" s="6">
-        <v>44927</v>
+        <v>330</v>
+      </c>
+      <c r="H97" s="5">
+        <v>42580</v>
       </c>
       <c r="I97" s="2">
         <v>5</v>
@@ -6103,46 +6474,49 @@
       <c r="J97" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K97" s="6">
+      <c r="K97" s="5">
         <v>40163</v>
       </c>
-      <c r="L97" s="6">
+      <c r="L97" s="5">
         <v>31761</v>
       </c>
-      <c r="M97" s="6">
+      <c r="M97" s="5">
         <v>52232</v>
       </c>
       <c r="N97" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="O97" s="6">
+        <v>346</v>
+      </c>
+      <c r="O97" s="5">
         <v>47114</v>
       </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P97" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B98" s="3" t="s">
-        <v>210</v>
+        <v>347</v>
       </c>
       <c r="C98" s="2">
         <v>70256</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D98" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F98" s="4" t="s">
-        <v>209</v>
+      <c r="F98" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H98" s="6">
-        <v>44927</v>
+        <v>330</v>
+      </c>
+      <c r="H98" s="5">
+        <v>43356</v>
       </c>
       <c r="I98" s="2">
         <v>5</v>
@@ -6150,45 +6524,48 @@
       <c r="J98" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K98" s="6">
-        <v>42380</v>
-      </c>
-      <c r="L98" s="6">
-        <v>34486</v>
-      </c>
-      <c r="M98" s="6">
-        <v>54970</v>
+      <c r="K98" s="5">
+        <v>42675</v>
+      </c>
+      <c r="L98" s="5">
+        <v>34340</v>
+      </c>
+      <c r="M98" s="5">
+        <v>54820</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="O98" s="6">
+        <v>348</v>
+      </c>
+      <c r="O98" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P98" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>211</v>
+        <v>349</v>
       </c>
       <c r="C99" s="2">
         <v>70255</v>
       </c>
-      <c r="D99" s="3" t="s">
+      <c r="D99" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E99" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F99" s="4" t="s">
-        <v>209</v>
+      <c r="F99" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H99" s="6">
+        <v>330</v>
+      </c>
+      <c r="H99" s="5">
         <v>45271</v>
       </c>
       <c r="I99" s="2">
@@ -6197,45 +6574,48 @@
       <c r="J99" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K99" s="6">
-        <v>42380</v>
-      </c>
-      <c r="L99" s="6">
+      <c r="K99" s="5">
+        <v>42675</v>
+      </c>
+      <c r="L99" s="5">
         <v>35819</v>
       </c>
-      <c r="M99" s="6">
+      <c r="M99" s="5">
         <v>56281</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="O99" s="6">
+        <v>350</v>
+      </c>
+      <c r="O99" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P99" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>212</v>
+        <v>351</v>
       </c>
       <c r="C100" s="2">
         <v>69835</v>
       </c>
-      <c r="D100" s="3" t="s">
+      <c r="D100" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E100" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F100" s="4" t="s">
-        <v>209</v>
+      <c r="F100" s="7" t="s">
+        <v>345</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H100" s="6">
+        <v>330</v>
+      </c>
+      <c r="H100" s="5">
         <v>44963</v>
       </c>
       <c r="I100" s="2">
@@ -6244,46 +6624,49 @@
       <c r="J100" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K100" s="6">
+      <c r="K100" s="5">
         <v>42597</v>
       </c>
-      <c r="L100" s="6">
+      <c r="L100" s="5">
         <v>35566</v>
       </c>
-      <c r="M100" s="6">
+      <c r="M100" s="5">
         <v>56036</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="O100" s="6">
+        <v>352</v>
+      </c>
+      <c r="O100" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P100" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>213</v>
+        <v>353</v>
       </c>
       <c r="C101" s="2">
         <v>46303</v>
       </c>
-      <c r="D101" s="3" t="s">
+      <c r="D101" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E101" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F101" s="4" t="s">
-        <v>214</v>
+      <c r="F101" s="7" t="s">
+        <v>354</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H101" s="6">
-        <v>46068</v>
+        <v>355</v>
+      </c>
+      <c r="H101" s="5">
+        <v>44743</v>
       </c>
       <c r="I101" s="2">
         <v>8</v>
@@ -6291,40 +6674,49 @@
       <c r="J101" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K101" s="6">
+      <c r="K101" s="5">
         <v>35490</v>
       </c>
-      <c r="L101" s="6">
+      <c r="L101" s="5">
         <v>28158</v>
       </c>
-      <c r="M101" s="6">
+      <c r="M101" s="5">
         <v>48639</v>
       </c>
-    </row>
-    <row r="102" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="N101" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="O101" s="5">
+        <v>47324</v>
+      </c>
+      <c r="P101" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>216</v>
+        <v>357</v>
       </c>
       <c r="C102" s="2">
         <v>49758</v>
       </c>
-      <c r="D102" s="3" t="s">
+      <c r="D102" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F102" s="4" t="s">
-        <v>217</v>
+      <c r="F102" s="7" t="s">
+        <v>358</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H102" s="6">
-        <v>44927</v>
+        <v>355</v>
+      </c>
+      <c r="H102" s="5">
+        <v>42781</v>
       </c>
       <c r="I102" s="2">
         <v>7</v>
@@ -6332,46 +6724,49 @@
       <c r="J102" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K102" s="6">
-        <v>39093</v>
-      </c>
-      <c r="L102" s="6">
+      <c r="K102" s="5">
+        <v>39387</v>
+      </c>
+      <c r="L102" s="5">
         <v>31275</v>
       </c>
-      <c r="M102" s="6">
+      <c r="M102" s="5">
         <v>51745</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="O102" s="6">
+        <v>359</v>
+      </c>
+      <c r="O102" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="103" spans="1:15" ht="26.25" x14ac:dyDescent="0.45">
+      <c r="P102" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>218</v>
+        <v>360</v>
       </c>
       <c r="C103" s="2">
         <v>53008</v>
       </c>
-      <c r="D103" s="3" t="s">
+      <c r="D103" s="2" t="s">
         <v>32</v>
       </c>
       <c r="E103" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F103" s="4" t="s">
-        <v>219</v>
+      <c r="F103" s="7" t="s">
+        <v>361</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H103" s="6">
-        <v>44927</v>
+        <v>355</v>
+      </c>
+      <c r="H103" s="5">
+        <v>43922</v>
       </c>
       <c r="I103" s="2">
         <v>7</v>
@@ -6379,46 +6774,49 @@
       <c r="J103" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K103" s="6">
+      <c r="K103" s="5">
         <v>39814</v>
       </c>
-      <c r="L103" s="6">
+      <c r="L103" s="5">
         <v>32826</v>
       </c>
-      <c r="M103" s="6">
+      <c r="M103" s="5">
         <v>53297</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="O103" s="6">
+        <v>362</v>
+      </c>
+      <c r="O103" s="5">
         <v>47285</v>
       </c>
-    </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P103" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>220</v>
+        <v>363</v>
       </c>
       <c r="C104" s="2">
         <v>71303</v>
       </c>
-      <c r="D104" s="3" t="s">
+      <c r="D104" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E104" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F104" s="4" t="s">
-        <v>221</v>
+      <c r="F104" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H104" s="6">
-        <v>44927</v>
+        <v>355</v>
+      </c>
+      <c r="H104" s="5">
+        <v>43466</v>
       </c>
       <c r="I104" s="2">
         <v>5</v>
@@ -6426,45 +6824,48 @@
       <c r="J104" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K104" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L104" s="6">
+      <c r="K104" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L104" s="5">
         <v>34055</v>
       </c>
-      <c r="M104" s="6">
+      <c r="M104" s="5">
         <v>54514</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="O104" s="6">
+        <v>365</v>
+      </c>
+      <c r="O104" s="5">
         <v>46407</v>
       </c>
-    </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P104" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A105" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>222</v>
+        <v>366</v>
       </c>
       <c r="C105" s="2">
         <v>74284</v>
       </c>
-      <c r="D105" s="3" t="s">
+      <c r="D105" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E105" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F105" s="4" t="s">
-        <v>221</v>
+      <c r="F105" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H105" s="6">
+        <v>355</v>
+      </c>
+      <c r="H105" s="5">
         <v>45566</v>
       </c>
       <c r="I105" s="2">
@@ -6473,45 +6874,48 @@
       <c r="J105" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K105" s="6">
+      <c r="K105" s="5">
         <v>44652</v>
       </c>
-      <c r="L105" s="6">
+      <c r="L105" s="5">
         <v>36293</v>
       </c>
-      <c r="M105" s="6">
+      <c r="M105" s="5">
         <v>56766</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="O105" s="6">
+        <v>367</v>
+      </c>
+      <c r="O105" s="5">
         <v>47114</v>
       </c>
-    </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P105" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>223</v>
+        <v>368</v>
       </c>
       <c r="C106" s="2">
         <v>74345</v>
       </c>
-      <c r="D106" s="3" t="s">
+      <c r="D106" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F106" s="4" t="s">
-        <v>221</v>
+      <c r="F106" s="7" t="s">
+        <v>364</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H106" s="6">
+        <v>355</v>
+      </c>
+      <c r="H106" s="5">
         <v>45566</v>
       </c>
       <c r="I106" s="2">
@@ -6520,39 +6924,48 @@
       <c r="J106" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="K106" s="6">
+      <c r="K106" s="5">
         <v>44774</v>
       </c>
-      <c r="L106" s="6">
+      <c r="L106" s="5">
         <v>35709</v>
       </c>
-      <c r="M106" s="6">
+      <c r="M106" s="5">
         <v>56189</v>
       </c>
-    </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="N106" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="O106" s="5">
+        <v>47114</v>
+      </c>
+      <c r="P106" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>224</v>
+        <v>370</v>
       </c>
       <c r="C107" s="2">
         <v>76642</v>
       </c>
-      <c r="D107" s="3" t="s">
+      <c r="D107" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F107" s="4" t="s">
-        <v>225</v>
+      <c r="F107" s="7" t="s">
+        <v>371</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H107" s="6">
+        <v>355</v>
+      </c>
+      <c r="H107" s="5">
         <v>45748</v>
       </c>
       <c r="I107" s="2">
@@ -6561,46 +6974,49 @@
       <c r="J107" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K107" s="6">
+      <c r="K107" s="5">
         <v>45250</v>
       </c>
-      <c r="L107" s="6">
+      <c r="L107" s="5">
         <v>38284</v>
       </c>
-      <c r="M107" s="6">
+      <c r="M107" s="5">
         <v>58746</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="O107" s="6">
+        <v>372</v>
+      </c>
+      <c r="O107" s="5">
         <v>47370</v>
       </c>
-    </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P107" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>226</v>
+        <v>373</v>
       </c>
       <c r="C108" s="2">
         <v>48252</v>
       </c>
-      <c r="D108" s="3" t="s">
+      <c r="D108" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F108" s="4" t="s">
-        <v>225</v>
+      <c r="F108" s="7" t="s">
+        <v>371</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H108" s="6">
-        <v>44927</v>
+        <v>355</v>
+      </c>
+      <c r="H108" s="5">
+        <v>42005</v>
       </c>
       <c r="I108" s="2">
         <v>5</v>
@@ -6608,46 +7024,49 @@
       <c r="J108" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K108" s="6">
-        <v>36900</v>
-      </c>
-      <c r="L108" s="6">
-        <v>28127</v>
-      </c>
-      <c r="M108" s="6">
-        <v>48611</v>
+      <c r="K108" s="5">
+        <v>37135</v>
+      </c>
+      <c r="L108" s="5">
+        <v>28157</v>
+      </c>
+      <c r="M108" s="5">
+        <v>48639</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="O108" s="6">
+        <v>374</v>
+      </c>
+      <c r="O108" s="5">
         <v>47265</v>
       </c>
-    </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.45">
+      <c r="P108" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>227</v>
+        <v>375</v>
       </c>
       <c r="C109" s="2">
         <v>71127</v>
       </c>
-      <c r="D109" s="3" t="s">
+      <c r="D109" s="2" t="s">
         <v>33</v>
       </c>
       <c r="E109" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F109" s="4" t="s">
-        <v>225</v>
+      <c r="F109" s="7" t="s">
+        <v>371</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H109" s="6">
-        <v>44927</v>
+        <v>355</v>
+      </c>
+      <c r="H109" s="5">
+        <v>44136</v>
       </c>
       <c r="I109" s="2">
         <v>5</v>
@@ -6655,46 +7074,158 @@
       <c r="J109" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="K109" s="6">
-        <v>42898</v>
-      </c>
-      <c r="L109" s="6">
+      <c r="K109" s="5">
+        <v>43075</v>
+      </c>
+      <c r="L109" s="5">
         <v>33830</v>
       </c>
-      <c r="M109" s="6">
+      <c r="M109" s="5">
         <v>54302</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="O109" s="6">
+        <v>376</v>
+      </c>
+      <c r="O109" s="5">
         <v>46407</v>
       </c>
-    </row>
+      <c r="P109" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.45"/>
+    <row r="113" x14ac:dyDescent="0.45"/>
+    <row r="114" x14ac:dyDescent="0.45"/>
+    <row r="115" x14ac:dyDescent="0.45"/>
+    <row r="116" x14ac:dyDescent="0.45"/>
+    <row r="117" x14ac:dyDescent="0.45"/>
+    <row r="118" x14ac:dyDescent="0.45"/>
+    <row r="119" x14ac:dyDescent="0.45"/>
+    <row r="120" x14ac:dyDescent="0.45"/>
+    <row r="121" x14ac:dyDescent="0.45"/>
+    <row r="122" x14ac:dyDescent="0.45"/>
+    <row r="123" x14ac:dyDescent="0.45"/>
+    <row r="124" x14ac:dyDescent="0.45"/>
+    <row r="125" x14ac:dyDescent="0.45"/>
+    <row r="126" x14ac:dyDescent="0.45"/>
+    <row r="127" x14ac:dyDescent="0.45"/>
+    <row r="128" x14ac:dyDescent="0.45"/>
+    <row r="129" x14ac:dyDescent="0.45"/>
+    <row r="130" x14ac:dyDescent="0.45"/>
+    <row r="131" x14ac:dyDescent="0.45"/>
+    <row r="132" x14ac:dyDescent="0.45"/>
+    <row r="133" x14ac:dyDescent="0.45"/>
+    <row r="134" x14ac:dyDescent="0.45"/>
+    <row r="135" x14ac:dyDescent="0.45"/>
+    <row r="136" x14ac:dyDescent="0.45"/>
+    <row r="137" x14ac:dyDescent="0.45"/>
+    <row r="138" x14ac:dyDescent="0.45"/>
+    <row r="139" x14ac:dyDescent="0.45"/>
+    <row r="140" x14ac:dyDescent="0.45"/>
+    <row r="141" x14ac:dyDescent="0.45"/>
+    <row r="142" x14ac:dyDescent="0.45"/>
+    <row r="143" x14ac:dyDescent="0.45"/>
+    <row r="144" x14ac:dyDescent="0.45"/>
+    <row r="145" x14ac:dyDescent="0.45"/>
+    <row r="146" x14ac:dyDescent="0.45"/>
+    <row r="147" x14ac:dyDescent="0.45"/>
+    <row r="148" x14ac:dyDescent="0.45"/>
+    <row r="149" x14ac:dyDescent="0.45"/>
+    <row r="150" x14ac:dyDescent="0.45"/>
+    <row r="151" x14ac:dyDescent="0.45"/>
+    <row r="152" x14ac:dyDescent="0.45"/>
+    <row r="153" x14ac:dyDescent="0.45"/>
+    <row r="154" x14ac:dyDescent="0.45"/>
+    <row r="155" x14ac:dyDescent="0.45"/>
+    <row r="156" x14ac:dyDescent="0.45"/>
+    <row r="157" x14ac:dyDescent="0.45"/>
+    <row r="158" x14ac:dyDescent="0.45"/>
+    <row r="159" x14ac:dyDescent="0.45"/>
+    <row r="160" x14ac:dyDescent="0.45"/>
+    <row r="161" x14ac:dyDescent="0.45"/>
+    <row r="162" x14ac:dyDescent="0.45"/>
+    <row r="163" x14ac:dyDescent="0.45"/>
+    <row r="164" x14ac:dyDescent="0.45"/>
+    <row r="165" x14ac:dyDescent="0.45"/>
+    <row r="166" x14ac:dyDescent="0.45"/>
+    <row r="167" x14ac:dyDescent="0.45"/>
+    <row r="168" x14ac:dyDescent="0.45"/>
+    <row r="169" x14ac:dyDescent="0.45"/>
+    <row r="170" x14ac:dyDescent="0.45"/>
+    <row r="171" x14ac:dyDescent="0.45"/>
+    <row r="172" x14ac:dyDescent="0.45"/>
+    <row r="173" x14ac:dyDescent="0.45"/>
+    <row r="174" x14ac:dyDescent="0.45"/>
+    <row r="175" x14ac:dyDescent="0.45"/>
+    <row r="176" x14ac:dyDescent="0.45"/>
+    <row r="177" x14ac:dyDescent="0.45"/>
+    <row r="178" x14ac:dyDescent="0.45"/>
+    <row r="179" x14ac:dyDescent="0.45"/>
+    <row r="180" x14ac:dyDescent="0.45"/>
+    <row r="181" x14ac:dyDescent="0.45"/>
+    <row r="182" x14ac:dyDescent="0.45"/>
+    <row r="183" x14ac:dyDescent="0.45"/>
+    <row r="184" x14ac:dyDescent="0.45"/>
+    <row r="185" x14ac:dyDescent="0.45"/>
+    <row r="186" x14ac:dyDescent="0.45"/>
+    <row r="187" x14ac:dyDescent="0.45"/>
+    <row r="188" x14ac:dyDescent="0.45"/>
+    <row r="189" x14ac:dyDescent="0.45"/>
+    <row r="190" x14ac:dyDescent="0.45"/>
+    <row r="191" x14ac:dyDescent="0.45"/>
+    <row r="192" x14ac:dyDescent="0.45"/>
+    <row r="193" x14ac:dyDescent="0.45"/>
+    <row r="194" x14ac:dyDescent="0.45"/>
+    <row r="195" x14ac:dyDescent="0.45"/>
+    <row r="196" x14ac:dyDescent="0.45"/>
+    <row r="197" x14ac:dyDescent="0.45"/>
+    <row r="198" x14ac:dyDescent="0.45"/>
+    <row r="199" x14ac:dyDescent="0.45"/>
+    <row r="200" x14ac:dyDescent="0.45"/>
   </sheetData>
-  <autoFilter ref="A1:T142" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:T199" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$A$1:$A$9</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D988</xm:sqref>
+          <xm:sqref>D2:D986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$B$1:$B$6</xm:f>
           </x14:formula1>
-          <xm:sqref>J2:J988</xm:sqref>
+          <xm:sqref>J2:J986</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0000-000002000000}">
           <x14:formula1>
             <xm:f>LIST_DATA!$C$1:$C$15</xm:f>
           </x14:formula1>
-          <xm:sqref>I2:I988</xm:sqref>
+          <xm:sqref>I2:I986</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{354EFE19-C43E-4A2D-83B1-FD15C013476E}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$D:$D</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9DE71029-D453-4F4E-B557-CC5A72AEA9EB}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$E:$E</xm:f>
+          </x14:formula1>
+          <xm:sqref>P2:P200 S2:S200</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{262E53F9-7911-451D-88C9-1E420930ED84}">
+          <x14:formula1>
+            <xm:f>LIST_DATA!$F:$F</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E200</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6704,130 +7235,297 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="13.59765625" customWidth="1"/>
+    <col min="1" max="1" width="16.73046875" style="8" customWidth="1"/>
+    <col min="2" max="3" width="9.06640625" style="8"/>
+    <col min="4" max="4" width="14.46484375" style="8" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="6" max="6" width="49.53125" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="C1">
+      <c r="C1" s="8">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+      <c r="D1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A2" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+      <c r="D2" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="8">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="D3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4">
+      <c r="B4" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="8">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+      <c r="D4" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="8">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+      <c r="D5" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="8">
         <v>9</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+      <c r="D6" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="8">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+      <c r="D7" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="8">
         <v>11</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+      <c r="D8" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A9" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="8">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C10">
+      <c r="D9" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C10" s="8">
         <v>13</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C11">
+      <c r="D10" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C11" s="8">
         <v>14</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C12">
+      <c r="D11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="8">
         <v>15</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C13">
+      <c r="D12" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="8">
         <v>16</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C14">
+      <c r="D13" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="8">
         <v>17</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="C15">
+      <c r="D14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="C15" s="8">
         <v>18</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="D16" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="D17" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F18" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F19" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F20" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F21" s="8" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F22" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F23" s="8" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F24" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="25" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F25" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="4:6" x14ac:dyDescent="0.45">
+      <c r="F26" s="8" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
